--- a/unit8_device_tree/DTtoDriverMappingSequence.xlsx
+++ b/unit8_device_tree/DTtoDriverMappingSequence.xlsx
@@ -2,41 +2,31 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Linux\unit8_device_tree\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103CB3B8-ACF7-4944-81E9-DCB5B11E0328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E901E68D-517A-4FA3-A3F0-33683503444A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D7C1D78-4B2E-4CF6-8186-DB05BC79365C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="load_dt_to_device_node" sheetId="1" r:id="rId1"/>
+    <sheet name="device_node_to_platform_device" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="111">
   <si>
     <t>u-boot</t>
   </si>
@@ -232,12 +222,358 @@
       <t>);</t>
     </r>
   </si>
+  <si>
+    <t>const struct machine_desc * __init setup_machine_fdt(unsigned int dt_phys)</t>
+  </si>
+  <si>
+    <t>early_init_dt_scan_nodes();</t>
+  </si>
+  <si>
+    <t>void __init early_init_dt_scan_nodes(void)</t>
+  </si>
+  <si>
+    <t>of_scan_flat_dt(early_init_dt_scan_chosen, boot_command_line);</t>
+  </si>
+  <si>
+    <t>of_scan_flat_dt(early_init_dt_scan_root, NULL);</t>
+  </si>
+  <si>
+    <t>of_scan_flat_dt(early_init_dt_scan_memory, NULL);</t>
+  </si>
+  <si>
+    <t>unflatten_dt_nodes(blob, mem, dad, mynodes);</t>
+  </si>
+  <si>
+    <t>of_alias_scan(early_init_dt_alloc_memory_arch);</t>
+  </si>
+  <si>
+    <t>unittest_unflatten_overlay_base();</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>arch_call_rest_init();</t>
+  </si>
+  <si>
+    <t>void __init __weak arch_call_rest_init(void)</t>
+  </si>
+  <si>
+    <t>rest_init();</t>
+  </si>
+  <si>
+    <t>noinline void __ref rest_init(void)</t>
+  </si>
+  <si>
+    <t>pid = kernel_thread(kernel_init, NULL, CLONE_FS);</t>
+  </si>
+  <si>
+    <t>static int __ref kernel_init(void *unused)</t>
+  </si>
+  <si>
+    <t>kernel_init_freeable();</t>
+  </si>
+  <si>
+    <t>static noinline void __init kernel_init_freeable(void)</t>
+  </si>
+  <si>
+    <t>do_basic_setup();</t>
+  </si>
+  <si>
+    <t>static void __init do_basic_setup(void)</t>
+  </si>
+  <si>
+    <t>do_initcalls();</t>
+  </si>
+  <si>
+    <t>pid = kernel_thread(kthreadd, NULL, CLONE_FS | CLONE_FILES);</t>
+  </si>
+  <si>
+    <t>drivers\of\platform.c</t>
+  </si>
+  <si>
+    <t>static int __init of_platform_default_populate_init(void)</t>
+  </si>
+  <si>
+    <t>if (!of_have_populated_dt())</t>
+  </si>
+  <si>
+    <t>        return -ENODEV;</t>
+  </si>
+  <si>
+    <t>of_platform_default_populate(NULL, NULL, NULL);</t>
+  </si>
+  <si>
+    <t>int of_platform_default_populate(struct device_node *root,</t>
+  </si>
+  <si>
+    <t> const struct of_dev_auxdata *lookup,</t>
+  </si>
+  <si>
+    <t> struct device *parent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> lookup,parent);</t>
+  </si>
+  <si>
+    <t>            const struct of_device_id *matches,</t>
+  </si>
+  <si>
+    <t>            const struct of_dev_auxdata *lookup,</t>
+  </si>
+  <si>
+    <t>            struct device *parent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int of_platform_populate(struct device_node *root,</t>
+  </si>
+  <si>
+    <t>of_device_add(dev)</t>
+  </si>
+  <si>
+    <t>        }</t>
+  </si>
+  <si>
+    <t>    }</t>
+  </si>
+  <si>
+    <t>    for_each_child_of_node(root, child) {</t>
+  </si>
+  <si>
+    <t>        if (rc) {</t>
+  </si>
+  <si>
+    <t>            of_node_put(child);</t>
+  </si>
+  <si>
+    <t>            break;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        rc = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>of_platform_bus_create</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(child, matches, lookup, parent, true);</t>
+    </r>
+  </si>
+  <si>
+    <t>static int of_platform_bus_create(struct device_node *bus,</t>
+  </si>
+  <si>
+    <t>const struct of_device_id *matches,</t>
+  </si>
+  <si>
+    <t>const struct of_dev_auxdata *lookup,</t>
+  </si>
+  <si>
+    <t>struct device *parent, bool strict)</t>
+  </si>
+  <si>
+    <t>static struct platform_device *of_platform_device_create_pdata(</t>
+  </si>
+  <si>
+    <t>struct device_node *np,</t>
+  </si>
+  <si>
+    <t>const char *bus_id,</t>
+  </si>
+  <si>
+    <t>void *platform_data,</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> struct device *parent)</t>
+  </si>
+  <si>
+    <t>struct platform_device *dev;</t>
+  </si>
+  <si>
+    <t>drivers\base\core.c</t>
+  </si>
+  <si>
+    <t>return device_add(&amp;ofdev-&gt;dev);</t>
+  </si>
+  <si>
+    <t>int device_add(struct device *dev)</t>
+  </si>
+  <si>
+    <t>struct platform_device *of_device_alloc(struct device_node *np,</t>
+  </si>
+  <si>
+    <t>struct device *parent)</t>
+  </si>
+  <si>
+    <t>dev = platform_device_alloc("", PLATFORM_DEVID_NONE);</t>
+  </si>
+  <si>
+    <t>res = kcalloc(num_irq + num_reg, sizeof(*res), GFP_KERNEL);</t>
+  </si>
+  <si>
+    <t>dev-&gt;resource = res;</t>
+  </si>
+  <si>
+    <t>dev-&gt;dev.bus = &amp;platform_bus_type;</t>
+  </si>
+  <si>
+    <t>dev-&gt;dev.platform_data = platform_data;</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dev = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>of_platform_device_create_pdata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(bus, bus_id, platform_data, parent);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    return </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>of_platform_populate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(root, of_default_bus_match_table,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dev = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>of_device_alloc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(np, bus_id, parent);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>if (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>of_device_add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(dev) != 0)</t>
+    </r>
+  </si>
+  <si>
+    <t>dev-&gt;kobj.parent = kobj;</t>
+  </si>
+  <si>
+    <t>kobj = get_device_parent(dev, parent);</t>
+  </si>
+  <si>
+    <t>parent = get_device(dev-&gt;parent);</t>
+  </si>
+  <si>
+    <t>kobject_add(&amp;dev-&gt;kobj, dev-&gt;kobj.parent, NULL);</t>
+  </si>
+  <si>
+    <t>error = device_platform_notify(dev, KOBJ_ADD);</t>
+  </si>
+  <si>
+    <t>error = device_create_file(dev, &amp;dev_attr_uevent);</t>
+  </si>
+  <si>
+    <t>error = device_add_class_symlinks(dev);</t>
+  </si>
+  <si>
+    <t>error = device_add_attrs(dev);</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,8 +602,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -280,8 +629,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -381,21 +742,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -408,6 +800,25 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -424,6 +835,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,7 +864,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -501,13 +914,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -554,13 +967,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -607,13 +1020,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -660,13 +1073,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -713,13 +1126,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -737,8 +1150,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8382000" y="5791200"/>
-          <a:ext cx="3352800" cy="0"/>
+          <a:off x="3429000" y="3619500"/>
+          <a:ext cx="2743200" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -766,15 +1179,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -790,7 +1203,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7562850" y="3981450"/>
+          <a:off x="5943600" y="3981450"/>
           <a:ext cx="2057400" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -819,15 +1232,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>40</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>63</xdr:col>
+      <xdr:col>49</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -872,15 +1285,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>40</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>56</xdr:col>
+      <xdr:col>42</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -921,6 +1334,2015 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Straight Arrow Connector 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10972800" y="5419725"/>
+          <a:ext cx="1143000" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6350">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>72</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rectangular Callout 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15468600" y="4781550"/>
+          <a:ext cx="2057400" cy="904876"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -143551"/>
+            <a:gd name="adj2" fmla="val 81008"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="800"/>
+            <a:t>duyệt</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" baseline="0"/>
+            <a:t> qua các node và lưu vào các  biến toàn cục: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="800"/>
+            <a:t>boot_command_line</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="800"/>
+            <a:t>initrd_start</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="800"/>
+            <a:t>initrd_end</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="800"/>
+            <a:t>of_fdt_crc32, ...</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="Straight Arrow Connector 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="10972800" y="6696075"/>
+          <a:ext cx="1600200" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6350">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="Straight Arrow Connector 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="8458200" y="6877050"/>
+          <a:ext cx="2057400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6350">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>72</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Rectangular Callout 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15240000" y="6953249"/>
+          <a:ext cx="2057400" cy="466726"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -143551"/>
+            <a:gd name="adj2" fmla="val 81008"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Chuyển đổi Device Tree từ dạng phẳng (FDT blob) sang cấu trúc cây struct device_node</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="800" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>64</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="Rectangular Callout 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15316200" y="8762999"/>
+          <a:ext cx="2057400" cy="466726"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -143551"/>
+            <a:gd name="adj2" fmla="val 81008"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Thực</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> hiện duyệt qua từng node và lưu vào devide node đầu có địa chỉ of_root</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="800" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="Straight Arrow Connector 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="8229600" y="10496550"/>
+          <a:ext cx="3657600" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6350">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="29" name="Straight Arrow Connector 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5486400" y="10677525"/>
+          <a:ext cx="2057400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6350">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Rectangular Callout 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3200400" y="12925425"/>
+          <a:ext cx="1828800" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 106449"/>
+            <a:gd name="adj2" fmla="val -35121"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>khởi</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> tạo thread đầu tiên</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="800" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Rectangular Callout 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2743200" y="15420975"/>
+          <a:ext cx="1828800" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 135615"/>
+            <a:gd name="adj2" fmla="val 81008"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>khởi</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> tạo kthreadd, thread sẽ kiểm soát các thread về sau</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="800" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="Rectangular Callout 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3905250" y="14068424"/>
+          <a:ext cx="1828800" cy="962026"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 143428"/>
+            <a:gd name="adj2" fmla="val 59368"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>gọi tất cả các hàm đã được đặt trong các section </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>.initcall*.init</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>, theo thứ tự từ thấp đến cao</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>,trong đó</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> có </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>static int __init of_platform_default_populate_init(void)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="800" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="914400" y="723900"/>
+          <a:ext cx="1600200" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6350">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangular Callout 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4829175" y="942975"/>
+          <a:ext cx="1600200" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -65575"/>
+            <a:gd name="adj2" fmla="val 41425"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Kiểm</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> tra of_root đã được gán chưa</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="800" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangular Callout 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1485900" y="3886200"/>
+          <a:ext cx="1600200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 93949"/>
+            <a:gd name="adj2" fmla="val 28925"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0"/>
+            <a:t>gọi</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="800" b="0" baseline="0"/>
+            <a:t> đệ quy đến tất cả các node để tạo platform driver</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="800" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="Straight Arrow Connector 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5257800" y="9229725"/>
+          <a:ext cx="3886200" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="6350">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangular Callout 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68C823A3-EC91-46BD-84F9-6DD3A08793A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7362825" y="9467850"/>
+          <a:ext cx="1600200" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -67956"/>
+            <a:gd name="adj2" fmla="val 93508"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0"/>
+            <a:t>Khởi tạo một dev rỗng</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="800" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangular Callout 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A559CDD3-F1B7-4224-90E5-07E448039CCF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9134475" y="9820275"/>
+          <a:ext cx="1600200" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -67956"/>
+            <a:gd name="adj2" fmla="val 93508"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0"/>
+            <a:t>Gán giá trị cho struct resource trong dev</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="800" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Rectangular Callout 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22D60CBC-7E39-464E-9D72-A1BAACCEF5F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7534275" y="10772775"/>
+          <a:ext cx="1600200" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -78670"/>
+            <a:gd name="adj2" fmla="val 57610"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0"/>
+            <a:t>Gán giá trị cho </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>struct bus_type </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0"/>
+            <a:t>trong dev</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="800" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>161924</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>114299</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rectangular Callout 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE88A1D7-D836-4CFF-B23C-6EC3596B8E1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6791324" y="1695450"/>
+          <a:ext cx="1781175" cy="704850"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -67956"/>
+            <a:gd name="adj2" fmla="val 93508"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="1"/>
+            <a:t>✅ of_platform_populate()</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Điểm bắt đầu.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Gọi đệ quy of_platform_bus_create() cho từng node con.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>66674</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>85724</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rectangular Callout 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1972AB0-B7F0-452F-BED9-86494AFC3FBB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6696074" y="3314699"/>
+          <a:ext cx="3086101" cy="752475"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -67956"/>
+            <a:gd name="adj2" fmla="val 93508"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="1"/>
+            <a:t>✅ of_platform_bus_create()</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Kiểm tra compatible, OF_POPULATED_BUS</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Nếu là primecell thì gọi of_amba_device_create(), nếu không thì:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Gọi of_platform_device_create_pdata() để tạo platform_device</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>219074</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangular Callout 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAD08003-BDF8-4111-829F-F6571FF34E99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7077074" y="5810249"/>
+          <a:ext cx="3086101" cy="847726"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -68573"/>
+            <a:gd name="adj2" fmla="val 78901"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="1"/>
+            <a:t>✅ of_platform_device_create_pdata()</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Gọi of_device_alloc() để tạo platform_device</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Gán thêm DMA, platform_data</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Gán bus: dev-&gt;dev.bus = &amp;platform_bus_type</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Gọi of_device_add() → gọi device_add() → đăng ký thiết bị vào hệ thống</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>66674</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>47626</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rectangular Callout 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F540EB4-99F3-485E-9464-41FFA7DF30C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6743700" y="7848599"/>
+          <a:ext cx="2447926" cy="657226"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -68573"/>
+            <a:gd name="adj2" fmla="val 78901"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="1"/>
+            <a:t>✅ of_device_alloc()</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Cấp phát platform_device</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Lấy thông tin resource[] từ device_node (reg, irq)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Gán node, parent, đặt tên</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>57</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Rectangular Callout 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B88BABE7-3A94-454B-9421-E446BA37B158}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11487150" y="12315825"/>
+          <a:ext cx="1600200" cy="504825"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -78670"/>
+            <a:gd name="adj2" fmla="val 57610"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="0"/>
+            <a:t>lấy thông tin của device parent, thông tin file của parent trong /sys/devices</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="800" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>47623</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rectangular Callout 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AC80207-7D4B-4F88-9396-97D7BB56DF45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7162800" y="11449048"/>
+          <a:ext cx="2447926" cy="971551"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -113320"/>
+            <a:gd name="adj2" fmla="val 4604"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="1"/>
+            <a:t>✅ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>device_add()</a:t>
+          </a:r>
+          <a:endParaRPr lang="vi-VN" sz="800" b="1"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Tạo thiết bị trong </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="1"/>
+            <a:t>core kernel object model</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t> và liên kết với các subsystem như:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>bus_type (platform bus)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>class (nếu có)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>parent (thiết bị cha)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>driver (gán sau khi match)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>57</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Rectangular Callout 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA1A7E46-D73D-416C-A060-F34545E02C1D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11830050" y="13582650"/>
+          <a:ext cx="1314450" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -122148"/>
+            <a:gd name="adj2" fmla="val 53836"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Tạo thư mục con trong /sys/devices/</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="800" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>58</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>64</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Rectangular Callout 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A7F6FB2-67A1-4D6D-85AA-E5CA9F06D0B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13477875" y="14144625"/>
+          <a:ext cx="1314450" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -122148"/>
+            <a:gd name="adj2" fmla="val 53836"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Tạo các thuộc tính đi kèm</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="800" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1242,702 +3664,2773 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B82AC82-F7D4-4E70-BBA8-FAD24C1E1A7F}">
-  <dimension ref="B3:BQ56"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B3:BC109"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="3" spans="2:65">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="2:51">
+      <c r="B3" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="3"/>
-      <c r="M3" s="1" t="s">
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22"/>
+      <c r="L3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="3"/>
-      <c r="Z3" s="1" t="s">
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="22"/>
+      <c r="U3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="AA3" s="2"/>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="3"/>
-      <c r="AI3" s="1" t="s">
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="22"/>
+      <c r="AB3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="AJ3" s="2"/>
-      <c r="AK3" s="2"/>
-      <c r="AL3" s="2"/>
-      <c r="AM3" s="2"/>
-      <c r="AN3" s="2"/>
-      <c r="AO3" s="2"/>
-      <c r="AP3" s="3"/>
-      <c r="BA3" s="1" t="s">
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21"/>
+      <c r="AF3" s="21"/>
+      <c r="AG3" s="21"/>
+      <c r="AH3" s="21"/>
+      <c r="AI3" s="22"/>
+      <c r="AM3" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="BB3" s="2"/>
-      <c r="BC3" s="2"/>
-      <c r="BD3" s="2"/>
-      <c r="BE3" s="2"/>
-      <c r="BF3" s="2"/>
-      <c r="BG3" s="2"/>
-      <c r="BH3" s="7"/>
-      <c r="BJ3" s="6" t="s">
+      <c r="AN3" s="21"/>
+      <c r="AO3" s="21"/>
+      <c r="AP3" s="21"/>
+      <c r="AQ3" s="21"/>
+      <c r="AR3" s="21"/>
+      <c r="AS3" s="21"/>
+      <c r="AT3" s="4"/>
+      <c r="AV3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="BK3" s="10"/>
-      <c r="BL3" s="10"/>
-      <c r="BM3" s="7"/>
-    </row>
-    <row r="4" spans="2:65">
-      <c r="C4" s="4"/>
-      <c r="E4" t="s">
+      <c r="AW3" s="7"/>
+      <c r="AX3" s="7"/>
+      <c r="AY3" s="4"/>
+    </row>
+    <row r="4" spans="2:51">
+      <c r="C4" s="1"/>
+      <c r="D4" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AL4" s="4"/>
-      <c r="BD4" s="5"/>
-      <c r="BK4" s="5"/>
-    </row>
-    <row r="5" spans="2:65">
-      <c r="C5" s="4"/>
-      <c r="E5" t="s">
+      <c r="N4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="AE4" s="1"/>
+      <c r="AP4" s="2"/>
+      <c r="AW4" s="2"/>
+    </row>
+    <row r="5" spans="2:51">
+      <c r="C5" s="1"/>
+      <c r="D5" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="4"/>
-      <c r="AA5" s="4"/>
-      <c r="AL5" s="4"/>
-      <c r="BD5" s="4"/>
-      <c r="BK5" s="4"/>
-    </row>
-    <row r="6" spans="2:65">
-      <c r="C6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" t="s">
+      <c r="N5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AP5" s="1"/>
+      <c r="AW5" s="1"/>
+    </row>
+    <row r="6" spans="2:51">
+      <c r="C6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" t="s">
         <v>6</v>
       </c>
-      <c r="AA6" s="4"/>
-      <c r="AL6" s="4"/>
-      <c r="BD6" s="4"/>
-      <c r="BK6" s="4"/>
-    </row>
-    <row r="7" spans="2:65">
-      <c r="C7" s="4"/>
-      <c r="E7" s="12" t="s">
+      <c r="V6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AP6" s="1"/>
+      <c r="AW6" s="1"/>
+    </row>
+    <row r="7" spans="2:51">
+      <c r="C7" s="1"/>
+      <c r="E7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="11"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="7"/>
-      <c r="AA7" s="4"/>
-      <c r="AL7" s="4"/>
-      <c r="BD7" s="4"/>
-      <c r="BK7" s="4"/>
-    </row>
-    <row r="8" spans="2:65">
-      <c r="C8" s="4"/>
-      <c r="E8" s="12" t="s">
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="8"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="4"/>
+      <c r="V7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AP7" s="1"/>
+      <c r="AW7" s="1"/>
+    </row>
+    <row r="8" spans="2:51">
+      <c r="C8" s="1"/>
+      <c r="E8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="11"/>
-      <c r="O8" s="4"/>
-      <c r="AA8" s="4"/>
-      <c r="AL8" s="4"/>
-      <c r="BD8" s="4"/>
-      <c r="BK8" s="4"/>
-    </row>
-    <row r="9" spans="2:65">
-      <c r="C9" s="4"/>
-      <c r="O9" s="8" t="s">
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="8"/>
+      <c r="N8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="AE8" s="1"/>
+      <c r="AP8" s="1"/>
+      <c r="AW8" s="1"/>
+    </row>
+    <row r="9" spans="2:51">
+      <c r="C9" s="1"/>
+      <c r="N9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="AA9" s="4"/>
-      <c r="AL9" s="4"/>
-      <c r="BD9" s="4"/>
-      <c r="BK9" s="4"/>
-    </row>
-    <row r="10" spans="2:65">
-      <c r="C10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="7"/>
-      <c r="AA10" s="4"/>
-      <c r="AL10" s="4"/>
-      <c r="BD10" s="4"/>
-      <c r="BK10" s="4"/>
-    </row>
-    <row r="11" spans="2:65">
-      <c r="C11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="AA11" s="4"/>
-      <c r="AL11" s="4"/>
-      <c r="BD11" s="4"/>
-      <c r="BK11" s="4"/>
-    </row>
-    <row r="12" spans="2:65">
-      <c r="C12" s="4"/>
-      <c r="O12" s="8" t="s">
+      <c r="V9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AP9" s="1"/>
+      <c r="AW9" s="1"/>
+    </row>
+    <row r="10" spans="2:51">
+      <c r="C10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="4"/>
+      <c r="V10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AP10" s="1"/>
+      <c r="AW10" s="1"/>
+    </row>
+    <row r="11" spans="2:51">
+      <c r="C11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AP11" s="1"/>
+      <c r="AW11" s="1"/>
+    </row>
+    <row r="12" spans="2:51">
+      <c r="C12" s="1"/>
+      <c r="N12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="AA12" s="4"/>
-      <c r="AL12" s="4"/>
-      <c r="BD12" s="4"/>
-      <c r="BK12" s="4"/>
-    </row>
-    <row r="13" spans="2:65">
-      <c r="C13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="9" t="s">
+      <c r="V12" s="1"/>
+      <c r="AE12" s="1"/>
+      <c r="AP12" s="1"/>
+      <c r="AW12" s="1"/>
+    </row>
+    <row r="13" spans="2:51">
+      <c r="C13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="AA13" s="4"/>
-      <c r="AL13" s="4"/>
-      <c r="BD13" s="4"/>
-      <c r="BK13" s="4"/>
-    </row>
-    <row r="14" spans="2:65">
-      <c r="C14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="R14" s="9" t="s">
+      <c r="V13" s="1"/>
+      <c r="AE13" s="1"/>
+      <c r="AP13" s="1"/>
+      <c r="AW13" s="1"/>
+    </row>
+    <row r="14" spans="2:51">
+      <c r="C14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="Q14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="4"/>
-      <c r="AL14" s="4"/>
-      <c r="BD14" s="4"/>
-      <c r="BK14" s="4"/>
-    </row>
-    <row r="15" spans="2:65">
-      <c r="C15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="AA15" s="4"/>
-      <c r="AL15" s="4"/>
-      <c r="BD15" s="4"/>
-      <c r="BK15" s="4"/>
-    </row>
-    <row r="16" spans="2:65">
-      <c r="C16" s="4"/>
-      <c r="O16" s="8" t="s">
+      <c r="V14" s="1"/>
+      <c r="AE14" s="1"/>
+      <c r="AP14" s="1"/>
+      <c r="AW14" s="1"/>
+    </row>
+    <row r="15" spans="2:51">
+      <c r="C15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="AE15" s="1"/>
+      <c r="AP15" s="1"/>
+      <c r="AW15" s="1"/>
+    </row>
+    <row r="16" spans="2:51">
+      <c r="C16" s="1"/>
+      <c r="N16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AA16" s="4"/>
-      <c r="AL16" s="4"/>
-      <c r="BD16" s="4"/>
-      <c r="BK16" s="4"/>
-    </row>
-    <row r="17" spans="3:63">
-      <c r="C17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="9" t="s">
+      <c r="V16" s="1"/>
+      <c r="AE16" s="1"/>
+      <c r="AP16" s="1"/>
+      <c r="AW16" s="1"/>
+    </row>
+    <row r="17" spans="3:49">
+      <c r="C17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AA17" s="4"/>
-      <c r="AL17" s="4"/>
-      <c r="BD17" s="4"/>
-      <c r="BK17" s="4"/>
-    </row>
-    <row r="18" spans="3:63">
-      <c r="C18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="R18" s="9" t="s">
+      <c r="V17" s="1"/>
+      <c r="AE17" s="1"/>
+      <c r="AP17" s="1"/>
+      <c r="AW17" s="1"/>
+    </row>
+    <row r="18" spans="3:49">
+      <c r="C18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="Q18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AA18" s="4"/>
-      <c r="AL18" s="4"/>
-      <c r="BD18" s="4"/>
-      <c r="BK18" s="4"/>
-    </row>
-    <row r="19" spans="3:63">
-      <c r="C19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="AA19" s="4"/>
-      <c r="AL19" s="4"/>
-      <c r="BD19" s="4"/>
-      <c r="BK19" s="4"/>
-    </row>
-    <row r="20" spans="3:63">
-      <c r="C20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="R20" t="s">
+      <c r="V18" s="1"/>
+      <c r="AE18" s="1"/>
+      <c r="AP18" s="1"/>
+      <c r="AW18" s="1"/>
+    </row>
+    <row r="19" spans="3:49">
+      <c r="C19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AP19" s="1"/>
+      <c r="AW19" s="1"/>
+    </row>
+    <row r="20" spans="3:49" ht="15">
+      <c r="C20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="W20" t="s">
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15"/>
+      <c r="R20" s="16"/>
+      <c r="T20" t="s">
         <v>15</v>
       </c>
-      <c r="AA20" s="4"/>
-      <c r="AL20" s="4"/>
-      <c r="BD20" s="4"/>
-      <c r="BK20" s="4"/>
-    </row>
-    <row r="21" spans="3:63">
-      <c r="C21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="AA21" s="4"/>
-      <c r="AB21" s="6"/>
-      <c r="AC21" s="10"/>
-      <c r="AD21" s="10"/>
-      <c r="AE21" s="7"/>
-      <c r="AL21" s="4"/>
-      <c r="BD21" s="4"/>
-      <c r="BK21" s="4"/>
-    </row>
-    <row r="22" spans="3:63">
-      <c r="C22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="AA22" s="4"/>
-      <c r="AC22" s="5"/>
-      <c r="AD22" t="s">
+      <c r="V20" s="1"/>
+      <c r="AE20" s="1"/>
+      <c r="AP20" s="1"/>
+      <c r="AW20" s="1"/>
+    </row>
+    <row r="21" spans="3:49">
+      <c r="C21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+      <c r="Z21" s="4"/>
+      <c r="AE21" s="1"/>
+      <c r="AP21" s="1"/>
+      <c r="AW21" s="1"/>
+    </row>
+    <row r="22" spans="3:49">
+      <c r="C22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="X22" s="2"/>
+      <c r="AP22" s="1"/>
+      <c r="AW22" s="1"/>
+    </row>
+    <row r="23" spans="3:49">
+      <c r="C23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" t="s">
         <v>16</v>
       </c>
-      <c r="AM22" t="s">
+      <c r="AF23" t="s">
         <v>17</v>
       </c>
-      <c r="BD22" s="4"/>
-      <c r="BK22" s="4"/>
-    </row>
-    <row r="23" spans="3:63">
-      <c r="C23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="AA23" s="4"/>
-      <c r="AC23" s="4"/>
-      <c r="AL23" s="4"/>
-      <c r="AM23" s="6"/>
-      <c r="AN23" s="10"/>
-      <c r="AO23" s="10"/>
-      <c r="AP23" s="7"/>
-      <c r="BD23" s="4"/>
-      <c r="BK23" s="4"/>
-    </row>
-    <row r="24" spans="3:63">
-      <c r="C24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="AA24" s="4"/>
-      <c r="AC24" s="4"/>
-      <c r="AL24" s="4"/>
-      <c r="AN24" s="5"/>
-      <c r="BD24" s="4"/>
-      <c r="BK24" s="4"/>
-    </row>
-    <row r="25" spans="3:63">
-      <c r="C25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="AA25" s="4"/>
-      <c r="AC25" s="4"/>
-      <c r="AL25" s="4"/>
-      <c r="AN25" t="s">
+      <c r="AP23" s="1"/>
+      <c r="AW23" s="1"/>
+    </row>
+    <row r="24" spans="3:49">
+      <c r="C24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="7"/>
+      <c r="AH24" s="7"/>
+      <c r="AI24" s="4"/>
+      <c r="AP24" s="1"/>
+      <c r="AW24" s="1"/>
+    </row>
+    <row r="25" spans="3:49">
+      <c r="C25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="AE25" s="1"/>
+      <c r="AG25" s="2"/>
+      <c r="AP25" s="1"/>
+      <c r="AW25" s="1"/>
+    </row>
+    <row r="26" spans="3:49">
+      <c r="C26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AG26" t="s">
         <v>28</v>
       </c>
-      <c r="BD25" s="4"/>
-      <c r="BK25" s="4"/>
-    </row>
-    <row r="26" spans="3:63">
-      <c r="C26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="AA26" s="4"/>
-      <c r="AC26" s="4"/>
-      <c r="AL26" s="4"/>
-      <c r="AN26" s="4" t="s">
+      <c r="AP26" s="1"/>
+      <c r="AW26" s="1"/>
+    </row>
+    <row r="27" spans="3:49">
+      <c r="C27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="X27" s="1"/>
+      <c r="AE27" s="1"/>
+      <c r="AG27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BD26" s="4"/>
-      <c r="BK26" s="4"/>
-    </row>
-    <row r="27" spans="3:63">
-      <c r="C27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="AA27" s="4"/>
-      <c r="AC27" s="4"/>
-      <c r="AL27" s="4"/>
-      <c r="AN27" s="4"/>
-      <c r="BD27" s="4"/>
-      <c r="BK27" s="4"/>
-    </row>
-    <row r="28" spans="3:63">
-      <c r="C28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="AA28" s="4"/>
-      <c r="AC28" s="4"/>
-      <c r="AL28" s="4"/>
-      <c r="AN28" s="4"/>
-      <c r="BD28" s="4"/>
-      <c r="BK28" s="4"/>
-    </row>
-    <row r="29" spans="3:63">
-      <c r="C29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="AA29" s="4"/>
-      <c r="AC29" s="4"/>
-      <c r="AL29" s="4"/>
-      <c r="AN29" s="4"/>
-      <c r="BD29" s="4"/>
-      <c r="BK29" s="4"/>
-    </row>
-    <row r="30" spans="3:63">
-      <c r="C30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="AA30" s="4"/>
-      <c r="AC30" s="4"/>
-      <c r="AL30" s="4"/>
-      <c r="AN30" s="4"/>
-      <c r="BD30" s="4"/>
-      <c r="BK30" s="4"/>
-    </row>
-    <row r="31" spans="3:63">
-      <c r="C31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="AA31" s="4"/>
-      <c r="AC31" s="4"/>
-      <c r="AL31" s="4"/>
-      <c r="AN31" s="4"/>
-      <c r="BD31" s="4"/>
-      <c r="BK31" s="4"/>
-    </row>
-    <row r="32" spans="3:63">
-      <c r="C32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="AA32" s="4"/>
-      <c r="AC32" s="4"/>
-      <c r="AL32" s="4"/>
-      <c r="AN32" s="4"/>
-      <c r="BD32" s="4"/>
-      <c r="BK32" s="4"/>
-    </row>
-    <row r="33" spans="3:69">
-      <c r="C33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="AA33" s="4"/>
-      <c r="AC33" s="4"/>
-      <c r="AL33" s="4"/>
-      <c r="AN33" s="4"/>
-      <c r="BD33" s="4"/>
-      <c r="BK33" s="4"/>
-    </row>
-    <row r="34" spans="3:69">
-      <c r="C34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="AA34" s="4"/>
-      <c r="AC34" s="4"/>
-      <c r="AL34" s="4"/>
-      <c r="AN34" s="4"/>
-      <c r="BD34" s="4"/>
-      <c r="BK34" s="4"/>
-    </row>
-    <row r="35" spans="3:69">
-      <c r="C35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="AA35" s="4"/>
-      <c r="AC35" s="4"/>
-      <c r="AL35" s="4"/>
-      <c r="AN35" s="4" t="s">
+      <c r="AP27" s="1"/>
+      <c r="AW27" s="1"/>
+    </row>
+    <row r="28" spans="3:49">
+      <c r="C28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AG28" s="1"/>
+      <c r="AO28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AP28" s="1"/>
+      <c r="AW28" s="1"/>
+    </row>
+    <row r="29" spans="3:49">
+      <c r="C29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AG29" s="1"/>
+      <c r="AP29" s="1"/>
+      <c r="AQ29" s="3"/>
+      <c r="AR29" s="7"/>
+      <c r="AS29" s="7"/>
+      <c r="AT29" s="4"/>
+      <c r="AW29" s="1"/>
+    </row>
+    <row r="30" spans="3:49">
+      <c r="C30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="AE30" s="1"/>
+      <c r="AG30" s="1"/>
+      <c r="AP30" s="1"/>
+      <c r="AQ30" s="11"/>
+      <c r="AR30" s="2"/>
+      <c r="AT30" s="10"/>
+      <c r="AW30" s="1"/>
+    </row>
+    <row r="31" spans="3:49">
+      <c r="C31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AG31" s="1"/>
+      <c r="AP31" s="1"/>
+      <c r="AQ31" s="12"/>
+      <c r="AR31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW31" s="1"/>
+    </row>
+    <row r="32" spans="3:49">
+      <c r="C32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AG32" s="1"/>
+      <c r="AP32" s="1"/>
+      <c r="AQ32" s="12"/>
+      <c r="AR32" s="1"/>
+      <c r="AW32" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="3:53">
+      <c r="C33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="AE33" s="1"/>
+      <c r="AG33" s="1"/>
+      <c r="AP33" s="1"/>
+      <c r="AQ33" s="12"/>
+      <c r="AR33" s="1"/>
+      <c r="AW33" s="1"/>
+      <c r="AX33" s="3"/>
+      <c r="AY33" s="7"/>
+      <c r="AZ33" s="7"/>
+      <c r="BA33" s="4"/>
+    </row>
+    <row r="34" spans="3:53">
+      <c r="C34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="AE34" s="1"/>
+      <c r="AG34" s="1"/>
+      <c r="AP34" s="1"/>
+      <c r="AR34" s="1"/>
+      <c r="AW34" s="1"/>
+      <c r="AY34" s="2"/>
+    </row>
+    <row r="35" spans="3:53">
+      <c r="C35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="X35" s="1"/>
+      <c r="AE35" s="1"/>
+      <c r="AG35" s="1"/>
+      <c r="AP35" s="1"/>
+      <c r="AR35" s="1"/>
+      <c r="AW35" s="1"/>
+      <c r="AY35" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="3:53">
+      <c r="C36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="AE36" s="1"/>
+      <c r="AG36" s="1"/>
+      <c r="AP36" s="1"/>
+      <c r="AR36" s="1"/>
+      <c r="AW36" s="1"/>
+      <c r="AY36" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="3:53">
+      <c r="C37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="X37" s="1"/>
+      <c r="AE37" s="1"/>
+      <c r="AG37" s="1"/>
+      <c r="AP37" s="1"/>
+      <c r="AR37" s="1"/>
+      <c r="AW37" s="1"/>
+      <c r="AY37" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="3:53">
+      <c r="C38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="X38" s="1"/>
+      <c r="AE38" s="1"/>
+      <c r="AG38" s="1"/>
+      <c r="AP38" s="1"/>
+      <c r="AR38" s="1"/>
+      <c r="AW38" s="1"/>
+      <c r="AY38" s="1"/>
+    </row>
+    <row r="39" spans="3:53">
+      <c r="C39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="AE39" s="1"/>
+      <c r="AG39" s="1"/>
+      <c r="AP39" s="1"/>
+      <c r="AR39" s="1"/>
+      <c r="AW39" s="1"/>
+    </row>
+    <row r="40" spans="3:53">
+      <c r="C40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="AE40" s="1"/>
+      <c r="AG40" s="1"/>
+      <c r="AP40" s="1"/>
+      <c r="AQ40" s="11"/>
+      <c r="AR40" s="10"/>
+      <c r="AW40" s="1"/>
+    </row>
+    <row r="41" spans="3:53">
+      <c r="C41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="X41" s="1"/>
+      <c r="AE41" s="1"/>
+      <c r="AG41" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="BD35" s="4"/>
-      <c r="BK35" s="4" t="s">
+      <c r="AP41" s="1"/>
+      <c r="AW41" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="3:69">
-      <c r="C36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="AA36" s="4"/>
-      <c r="AC36" s="4"/>
-      <c r="AL36" s="4"/>
-      <c r="AN36" s="4"/>
-      <c r="BD36" s="4"/>
-      <c r="BK36" s="4"/>
-      <c r="BL36" s="6"/>
-      <c r="BM36" s="10"/>
-      <c r="BN36" s="10"/>
-      <c r="BO36" s="7"/>
-    </row>
-    <row r="37" spans="3:69">
-      <c r="C37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="AA37" s="4"/>
-      <c r="AC37" s="4"/>
-      <c r="AL37" s="4"/>
-      <c r="AN37" s="4"/>
-      <c r="BD37" s="4"/>
-      <c r="BK37" s="4"/>
-      <c r="BM37" s="5"/>
-    </row>
-    <row r="38" spans="3:69">
-      <c r="C38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="AA38" s="4"/>
-      <c r="AC38" s="4"/>
-      <c r="AL38" s="4"/>
-      <c r="AN38" s="4"/>
-      <c r="BD38" s="4"/>
-      <c r="BK38" s="4" t="s">
+    <row r="42" spans="3:53">
+      <c r="C42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="AE42" s="1"/>
+      <c r="AG42" s="1"/>
+      <c r="AP42" s="1"/>
+      <c r="AW42" s="1"/>
+      <c r="AX42" s="3"/>
+      <c r="AY42" s="7"/>
+      <c r="AZ42" s="7"/>
+      <c r="BA42" s="4"/>
+    </row>
+    <row r="43" spans="3:53">
+      <c r="C43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="X43" s="1"/>
+      <c r="AE43" s="1"/>
+      <c r="AG43" s="1"/>
+      <c r="AP43" s="1"/>
+      <c r="AW43" s="1"/>
+      <c r="AY43" s="2"/>
+    </row>
+    <row r="44" spans="3:53">
+      <c r="C44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="AE44" s="1"/>
+      <c r="AG44" s="1"/>
+      <c r="AP44" s="1"/>
+      <c r="AW44" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="BM38" s="4"/>
-    </row>
-    <row r="39" spans="3:69">
-      <c r="C39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="AA39" s="4"/>
-      <c r="AC39" s="4"/>
-      <c r="AL39" s="4"/>
-      <c r="AN39" s="4"/>
-      <c r="BD39" s="4"/>
-      <c r="BK39" s="4" t="s">
+      <c r="AY44" s="1"/>
+    </row>
+    <row r="45" spans="3:53">
+      <c r="C45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="AE45" s="1"/>
+      <c r="AG45" s="1"/>
+      <c r="AP45" s="1"/>
+      <c r="AW45" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="BM39" s="4"/>
-    </row>
-    <row r="40" spans="3:69">
-      <c r="C40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="AA40" s="4"/>
-      <c r="AC40" s="4"/>
-      <c r="AL40" s="4"/>
-      <c r="AN40" s="4"/>
-      <c r="BD40" s="4"/>
-      <c r="BK40" s="4"/>
-      <c r="BM40" s="4"/>
-    </row>
-    <row r="41" spans="3:69">
-      <c r="C41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="AA41" s="4"/>
-      <c r="AC41" s="4"/>
-      <c r="AL41" s="4"/>
-      <c r="AN41" s="4"/>
-      <c r="BD41" s="4"/>
-      <c r="BK41" s="4" t="s">
+      <c r="AY45" s="1"/>
+    </row>
+    <row r="46" spans="3:53">
+      <c r="C46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="V46" s="1"/>
+      <c r="X46" s="1"/>
+      <c r="AE46" s="1"/>
+      <c r="AG46" s="1"/>
+      <c r="AP46" s="1"/>
+      <c r="AW46" s="1"/>
+      <c r="AY46" s="1"/>
+    </row>
+    <row r="47" spans="3:53">
+      <c r="C47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="V47" s="1"/>
+      <c r="X47" s="1"/>
+      <c r="AE47" s="1"/>
+      <c r="AG47" s="1"/>
+      <c r="AP47" s="1"/>
+      <c r="AW47" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="BM41" s="4"/>
-    </row>
-    <row r="42" spans="3:69">
-      <c r="C42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="AA42" s="4"/>
-      <c r="AC42" s="4"/>
-      <c r="AL42" s="4"/>
-      <c r="AN42" s="4"/>
-      <c r="BD42" s="4"/>
-      <c r="BK42" s="4"/>
-      <c r="BM42" s="4" t="s">
+      <c r="AY47" s="1"/>
+    </row>
+    <row r="48" spans="3:53">
+      <c r="C48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="V48" s="1"/>
+      <c r="X48" s="1"/>
+      <c r="AE48" s="1"/>
+      <c r="AG48" s="1"/>
+      <c r="AP48" s="1"/>
+      <c r="AW48" s="1"/>
+      <c r="AY48" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="3:69">
-      <c r="C43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="AA43" s="4"/>
-      <c r="AC43" s="4"/>
-      <c r="AL43" s="4"/>
-      <c r="AN43" s="4"/>
-      <c r="BD43" s="4"/>
-      <c r="BK43" s="4"/>
-      <c r="BM43" s="4" t="s">
+    <row r="49" spans="3:55">
+      <c r="C49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="V49" s="1"/>
+      <c r="X49" s="1"/>
+      <c r="AE49" s="1"/>
+      <c r="AG49" s="1"/>
+      <c r="AP49" s="1"/>
+      <c r="AW49" s="1"/>
+      <c r="AY49" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="3:69">
-      <c r="C44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="AA44" s="4"/>
-      <c r="AC44" s="4"/>
-      <c r="AL44" s="4"/>
-      <c r="AN44" s="4"/>
-      <c r="BD44" s="4"/>
-      <c r="BK44" s="4"/>
-      <c r="BM44" s="4" t="s">
+    <row r="50" spans="3:55">
+      <c r="C50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="V50" s="1"/>
+      <c r="X50" s="1"/>
+      <c r="AE50" s="1"/>
+      <c r="AG50" s="1"/>
+      <c r="AP50" s="1"/>
+      <c r="AW50" s="1"/>
+      <c r="AY50" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="3:69">
-      <c r="C45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="AA45" s="4"/>
-      <c r="AC45" s="4"/>
-      <c r="AL45" s="4"/>
-      <c r="AN45" s="4"/>
-      <c r="BD45" s="4"/>
-      <c r="BK45" s="4"/>
-      <c r="BM45" s="4" t="s">
+    <row r="51" spans="3:55">
+      <c r="C51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="AE51" s="1"/>
+      <c r="AG51" s="1"/>
+      <c r="AP51" s="1"/>
+      <c r="AW51" s="1"/>
+      <c r="AY51" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="3:69">
-      <c r="C46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="AA46" s="4"/>
-      <c r="AC46" s="4"/>
-      <c r="AL46" s="4"/>
-      <c r="AN46" s="4"/>
-      <c r="BD46" s="4"/>
-      <c r="BK46" s="4"/>
-      <c r="BM46" s="4"/>
-      <c r="BN46" s="6"/>
-      <c r="BO46" s="10"/>
-      <c r="BP46" s="10"/>
-      <c r="BQ46" s="7"/>
-    </row>
-    <row r="47" spans="3:69">
-      <c r="C47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="AA47" s="4"/>
-      <c r="AC47" s="4"/>
-      <c r="AL47" s="4"/>
-      <c r="AN47" s="4"/>
-      <c r="BD47" s="4"/>
-      <c r="BK47" s="4"/>
-      <c r="BM47" s="4"/>
-      <c r="BO47" s="5"/>
-    </row>
-    <row r="48" spans="3:69">
-      <c r="C48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="AA48" s="4"/>
-      <c r="AC48" s="4"/>
-      <c r="AL48" s="4"/>
-      <c r="AN48" s="4"/>
-      <c r="BD48" s="4"/>
-      <c r="BK48" s="4"/>
-      <c r="BM48" s="4"/>
-      <c r="BO48" s="4"/>
-    </row>
-    <row r="49" spans="3:67">
-      <c r="C49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="AA49" s="4"/>
-      <c r="AC49" s="4"/>
-      <c r="AL49" s="4"/>
-      <c r="AN49" s="4"/>
-      <c r="BD49" s="4"/>
-      <c r="BK49" s="4"/>
-      <c r="BM49" s="4"/>
-      <c r="BO49" s="4"/>
-    </row>
-    <row r="50" spans="3:67">
-      <c r="C50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="AA50" s="4"/>
-      <c r="AC50" s="4"/>
-      <c r="AL50" s="4"/>
-      <c r="AN50" s="4"/>
-      <c r="BD50" s="4"/>
-      <c r="BK50" s="4"/>
-      <c r="BM50" s="4"/>
-      <c r="BO50" s="4"/>
-    </row>
-    <row r="51" spans="3:67">
-      <c r="C51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="AA51" s="4"/>
-      <c r="AC51" s="4"/>
-      <c r="AL51" s="4"/>
-      <c r="AN51" s="4"/>
-      <c r="BD51" s="4"/>
-      <c r="BK51" s="4"/>
-      <c r="BM51" s="4"/>
-      <c r="BO51" s="4"/>
-    </row>
-    <row r="52" spans="3:67">
-      <c r="C52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="AA52" s="4"/>
-      <c r="AC52" s="4"/>
-      <c r="AL52" s="4"/>
-      <c r="AN52" s="4"/>
-      <c r="BD52" s="4"/>
-      <c r="BK52" s="4"/>
-      <c r="BM52" s="4"/>
-      <c r="BO52" s="4"/>
-    </row>
-    <row r="53" spans="3:67">
-      <c r="C53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="AA53" s="4"/>
-      <c r="AC53" s="4"/>
-      <c r="AL53" s="4"/>
-      <c r="AN53" s="4"/>
-      <c r="BD53" s="4"/>
-      <c r="BK53" s="4"/>
-      <c r="BM53" s="4"/>
-      <c r="BO53" s="4"/>
-    </row>
-    <row r="54" spans="3:67">
-      <c r="C54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="AA54" s="4"/>
-      <c r="AC54" s="4"/>
-      <c r="AL54" s="4"/>
-      <c r="AN54" s="4"/>
-      <c r="BD54" s="4"/>
-      <c r="BK54" s="4"/>
-      <c r="BM54" s="4"/>
-      <c r="BO54" s="4"/>
-    </row>
-    <row r="55" spans="3:67">
-      <c r="C55" s="4"/>
-      <c r="O55" s="4"/>
-      <c r="AA55" s="4"/>
-      <c r="AC55" s="4"/>
-      <c r="AL55" s="4"/>
-      <c r="AN55" s="4"/>
-      <c r="BD55" s="4"/>
-      <c r="BK55" s="4"/>
-      <c r="BM55" s="4"/>
-      <c r="BO55" s="4"/>
-    </row>
-    <row r="56" spans="3:67">
-      <c r="C56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="AA56" s="4"/>
-      <c r="AC56" s="4"/>
-      <c r="AL56" s="4"/>
-      <c r="AN56" s="4"/>
-      <c r="BD56" s="4"/>
-      <c r="BK56" s="4"/>
-      <c r="BM56" s="4"/>
-      <c r="BO56" s="4"/>
+    <row r="52" spans="3:55">
+      <c r="C52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="V52" s="1"/>
+      <c r="X52" s="1"/>
+      <c r="AE52" s="1"/>
+      <c r="AG52" s="1"/>
+      <c r="AP52" s="1"/>
+      <c r="AW52" s="1"/>
+      <c r="AY52" s="1"/>
+      <c r="AZ52" s="3"/>
+      <c r="BA52" s="7"/>
+      <c r="BB52" s="7"/>
+      <c r="BC52" s="4"/>
+    </row>
+    <row r="53" spans="3:55">
+      <c r="C53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="V53" s="1"/>
+      <c r="X53" s="1"/>
+      <c r="AE53" s="1"/>
+      <c r="AG53" s="1"/>
+      <c r="AP53" s="1"/>
+      <c r="AW53" s="1"/>
+      <c r="AY53" s="1"/>
+      <c r="BA53" s="2"/>
+    </row>
+    <row r="54" spans="3:55">
+      <c r="C54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="V54" s="1"/>
+      <c r="X54" s="1"/>
+      <c r="AE54" s="1"/>
+      <c r="AG54" s="1"/>
+      <c r="AP54" s="1"/>
+      <c r="AW54" s="1"/>
+      <c r="AY54" s="1"/>
+      <c r="BA54" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="3:55">
+      <c r="C55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="V55" s="1"/>
+      <c r="X55" s="1"/>
+      <c r="AE55" s="1"/>
+      <c r="AG55" s="1"/>
+      <c r="AP55" s="1"/>
+      <c r="AW55" s="1"/>
+      <c r="AY55" s="1"/>
+      <c r="AZ55" s="13"/>
+      <c r="BA55" s="14"/>
+    </row>
+    <row r="56" spans="3:55">
+      <c r="C56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="V56" s="1"/>
+      <c r="X56" s="1"/>
+      <c r="AE56" s="1"/>
+      <c r="AG56" s="1"/>
+      <c r="AP56" s="1"/>
+      <c r="AW56" s="1"/>
+      <c r="AY56" s="1"/>
+      <c r="BA56" s="10"/>
+    </row>
+    <row r="57" spans="3:55">
+      <c r="C57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="V57" s="1"/>
+      <c r="X57" s="1"/>
+      <c r="AE57" s="1"/>
+      <c r="AG57" s="1"/>
+      <c r="AP57" s="1"/>
+      <c r="AW57" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AY57" s="1"/>
+    </row>
+    <row r="58" spans="3:55">
+      <c r="C58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="V58" s="1"/>
+      <c r="X58" s="1"/>
+      <c r="AE58" s="1"/>
+      <c r="AG58" s="1"/>
+      <c r="AP58" s="1"/>
+      <c r="AW58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AY58" s="1"/>
+    </row>
+    <row r="59" spans="3:55">
+      <c r="C59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="V59" s="1"/>
+      <c r="X59" s="1"/>
+      <c r="AE59" s="1"/>
+      <c r="AG59" s="1"/>
+      <c r="AP59" s="1"/>
+      <c r="AW59" s="1"/>
+      <c r="AX59" s="13"/>
+      <c r="AY59" s="14"/>
+    </row>
+    <row r="60" spans="3:55">
+      <c r="C60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="V60" s="1"/>
+      <c r="X60" s="1"/>
+      <c r="AE60" s="1"/>
+      <c r="AG60" s="1"/>
+      <c r="AH60" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP60" s="1"/>
+      <c r="AW60" s="1"/>
+      <c r="AY60" s="10"/>
+    </row>
+    <row r="61" spans="3:55">
+      <c r="C61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="V61" s="1"/>
+      <c r="X61" s="1"/>
+      <c r="AE61" s="1"/>
+      <c r="AP61" s="1"/>
+      <c r="AW61" s="1"/>
+    </row>
+    <row r="62" spans="3:55" s="19" customFormat="1">
+      <c r="C62" s="18"/>
+      <c r="N62" s="18"/>
+      <c r="V62" s="18"/>
+      <c r="X62" s="18"/>
+      <c r="AE62" s="18"/>
+      <c r="AP62" s="18"/>
+      <c r="AW62" s="18"/>
+    </row>
+    <row r="63" spans="3:55">
+      <c r="C63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="V63" s="1"/>
+      <c r="X63" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP63" s="1"/>
+    </row>
+    <row r="64" spans="3:55">
+      <c r="C64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="V64" s="1"/>
+      <c r="X64" s="1"/>
+      <c r="AP64" s="1"/>
+    </row>
+    <row r="65" spans="3:42">
+      <c r="C65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="V65" s="1"/>
+      <c r="X65" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP65" s="1"/>
+    </row>
+    <row r="66" spans="3:42">
+      <c r="C66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="V66" s="1"/>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="7"/>
+      <c r="AA66" s="7"/>
+      <c r="AB66" s="4"/>
+      <c r="AP66" s="1"/>
+    </row>
+    <row r="67" spans="3:42">
+      <c r="C67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="V67" s="1"/>
+      <c r="X67" s="1"/>
+      <c r="Y67" s="11"/>
+      <c r="Z67" s="2"/>
+      <c r="AP67" s="1"/>
+    </row>
+    <row r="68" spans="3:42">
+      <c r="C68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="V68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="12"/>
+      <c r="Z68" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AP68" s="1"/>
+    </row>
+    <row r="69" spans="3:42">
+      <c r="C69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="V69" s="1"/>
+      <c r="X69" s="1"/>
+      <c r="Y69" s="12"/>
+      <c r="Z69" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP69" s="1"/>
+    </row>
+    <row r="70" spans="3:42">
+      <c r="C70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="V70" s="1"/>
+      <c r="X70" s="1"/>
+      <c r="Z70" s="1"/>
+      <c r="AA70" s="3"/>
+      <c r="AB70" s="7"/>
+      <c r="AC70" s="7"/>
+      <c r="AD70" s="4"/>
+      <c r="AP70" s="1"/>
+    </row>
+    <row r="71" spans="3:42">
+      <c r="C71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="V71" s="1"/>
+      <c r="X71" s="1"/>
+      <c r="Z71" s="1"/>
+      <c r="AB71" s="2"/>
+      <c r="AP71" s="1"/>
+    </row>
+    <row r="72" spans="3:42">
+      <c r="C72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="V72" s="1"/>
+      <c r="X72" s="1"/>
+      <c r="Z72" s="1"/>
+      <c r="AB72" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP72" s="1"/>
+    </row>
+    <row r="73" spans="3:42">
+      <c r="C73" s="1"/>
+      <c r="N73" s="1"/>
+      <c r="V73" s="1"/>
+      <c r="X73" s="1"/>
+      <c r="Z73" s="1"/>
+      <c r="AB73" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP73" s="1"/>
+    </row>
+    <row r="74" spans="3:42">
+      <c r="C74" s="1"/>
+      <c r="N74" s="1"/>
+      <c r="V74" s="1"/>
+      <c r="X74" s="1"/>
+      <c r="Z74" s="1"/>
+      <c r="AB74" s="1"/>
+      <c r="AC74" s="7"/>
+      <c r="AD74" s="7"/>
+      <c r="AE74" s="7"/>
+      <c r="AF74" s="4"/>
+      <c r="AP74" s="1"/>
+    </row>
+    <row r="75" spans="3:42">
+      <c r="C75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="V75" s="1"/>
+      <c r="X75" s="1"/>
+      <c r="Z75" s="1"/>
+      <c r="AB75" s="1"/>
+      <c r="AD75" s="2"/>
+      <c r="AP75" s="1"/>
+    </row>
+    <row r="76" spans="3:42">
+      <c r="C76" s="1"/>
+      <c r="N76" s="1"/>
+      <c r="V76" s="1"/>
+      <c r="X76" s="1"/>
+      <c r="Z76" s="1"/>
+      <c r="AB76" s="1"/>
+      <c r="AD76" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP76" s="1"/>
+    </row>
+    <row r="77" spans="3:42">
+      <c r="C77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="V77" s="1"/>
+      <c r="X77" s="1"/>
+      <c r="Z77" s="1"/>
+      <c r="AB77" s="1"/>
+      <c r="AD77" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AP77" s="1"/>
+    </row>
+    <row r="78" spans="3:42">
+      <c r="C78" s="1"/>
+      <c r="N78" s="1"/>
+      <c r="V78" s="1"/>
+      <c r="X78" s="1"/>
+      <c r="Z78" s="1"/>
+      <c r="AB78" s="1"/>
+      <c r="AD78" s="1"/>
+      <c r="AE78" s="3"/>
+      <c r="AF78" s="7"/>
+      <c r="AG78" s="7"/>
+      <c r="AH78" s="4"/>
+      <c r="AP78" s="1"/>
+    </row>
+    <row r="79" spans="3:42">
+      <c r="C79" s="1"/>
+      <c r="N79" s="1"/>
+      <c r="V79" s="1"/>
+      <c r="X79" s="1"/>
+      <c r="Z79" s="1"/>
+      <c r="AB79" s="1"/>
+      <c r="AD79" s="1"/>
+      <c r="AF79" s="2"/>
+      <c r="AP79" s="1"/>
+    </row>
+    <row r="80" spans="3:42">
+      <c r="C80" s="1"/>
+      <c r="N80" s="1"/>
+      <c r="V80" s="1"/>
+      <c r="X80" s="1"/>
+      <c r="Z80" s="1"/>
+      <c r="AB80" s="1"/>
+      <c r="AD80" s="1"/>
+      <c r="AF80" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP80" s="1"/>
+    </row>
+    <row r="81" spans="3:42">
+      <c r="C81" s="1"/>
+      <c r="N81" s="1"/>
+      <c r="V81" s="1"/>
+      <c r="X81" s="1"/>
+      <c r="Z81" s="1"/>
+      <c r="AB81" s="1"/>
+      <c r="AD81" s="1"/>
+      <c r="AF81" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP81" s="1"/>
+    </row>
+    <row r="82" spans="3:42">
+      <c r="C82" s="1"/>
+      <c r="N82" s="1"/>
+      <c r="V82" s="1"/>
+      <c r="X82" s="1"/>
+      <c r="Z82" s="1"/>
+      <c r="AB82" s="1"/>
+      <c r="AD82" s="1"/>
+      <c r="AF82" s="1"/>
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="7"/>
+      <c r="AI82" s="7"/>
+      <c r="AJ82" s="4"/>
+      <c r="AP82" s="1"/>
+    </row>
+    <row r="83" spans="3:42">
+      <c r="C83" s="1"/>
+      <c r="N83" s="1"/>
+      <c r="V83" s="1"/>
+      <c r="X83" s="1"/>
+      <c r="Z83" s="1"/>
+      <c r="AB83" s="1"/>
+      <c r="AD83" s="1"/>
+      <c r="AF83" s="1"/>
+      <c r="AH83" s="2"/>
+      <c r="AP83" s="1"/>
+    </row>
+    <row r="84" spans="3:42">
+      <c r="C84" s="1"/>
+      <c r="N84" s="1"/>
+      <c r="V84" s="1"/>
+      <c r="X84" s="1"/>
+      <c r="Z84" s="1"/>
+      <c r="AB84" s="1"/>
+      <c r="AD84" s="1"/>
+      <c r="AF84" s="1"/>
+      <c r="AH84" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AP84" s="1"/>
+    </row>
+    <row r="85" spans="3:42">
+      <c r="C85" s="1"/>
+      <c r="N85" s="1"/>
+      <c r="V85" s="1"/>
+      <c r="X85" s="1"/>
+      <c r="Z85" s="1"/>
+      <c r="AB85" s="1"/>
+      <c r="AD85" s="1"/>
+      <c r="AF85" s="1"/>
+      <c r="AG85" s="13"/>
+      <c r="AH85" s="14"/>
+      <c r="AP85" s="1"/>
+    </row>
+    <row r="86" spans="3:42">
+      <c r="C86" s="1"/>
+      <c r="N86" s="1"/>
+      <c r="V86" s="1"/>
+      <c r="X86" s="1"/>
+      <c r="Z86" s="1"/>
+      <c r="AB86" s="1"/>
+      <c r="AD86" s="1"/>
+      <c r="AE86" s="13"/>
+      <c r="AF86" s="14"/>
+      <c r="AH86" s="10"/>
+      <c r="AP86" s="1"/>
+    </row>
+    <row r="87" spans="3:42">
+      <c r="C87" s="1"/>
+      <c r="N87" s="1"/>
+      <c r="V87" s="1"/>
+      <c r="X87" s="1"/>
+      <c r="Z87" s="1"/>
+      <c r="AB87" s="1"/>
+      <c r="AC87" s="13"/>
+      <c r="AD87" s="14"/>
+      <c r="AP87" s="1"/>
+    </row>
+    <row r="88" spans="3:42">
+      <c r="C88" s="1"/>
+      <c r="N88" s="1"/>
+      <c r="V88" s="1"/>
+      <c r="X88" s="1"/>
+      <c r="Z88" s="1"/>
+      <c r="AA88" s="12"/>
+      <c r="AB88" s="1"/>
+      <c r="AP88" s="1"/>
+    </row>
+    <row r="89" spans="3:42">
+      <c r="C89" s="1"/>
+      <c r="N89" s="1"/>
+      <c r="V89" s="1"/>
+      <c r="X89" s="1"/>
+      <c r="Z89" s="1"/>
+      <c r="AA89" s="12"/>
+      <c r="AB89" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AP89" s="1"/>
+    </row>
+    <row r="90" spans="3:42">
+      <c r="C90" s="1"/>
+      <c r="N90" s="1"/>
+      <c r="V90" s="1"/>
+      <c r="X90" s="1"/>
+      <c r="Z90" s="1"/>
+      <c r="AA90" s="12"/>
+      <c r="AB90" s="1"/>
+      <c r="AC90" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP90" s="1"/>
+    </row>
+    <row r="91" spans="3:42">
+      <c r="C91" s="1"/>
+      <c r="N91" s="1"/>
+      <c r="V91" s="1"/>
+      <c r="X91" s="1"/>
+      <c r="Z91" s="1"/>
+      <c r="AA91" s="12"/>
+      <c r="AB91" s="1"/>
+      <c r="AP91" s="1"/>
+    </row>
+    <row r="92" spans="3:42">
+      <c r="C92" s="1"/>
+      <c r="N92" s="1"/>
+      <c r="V92" s="1"/>
+      <c r="X92" s="1"/>
+      <c r="Z92" s="1"/>
+      <c r="AA92" s="13"/>
+      <c r="AB92" s="14"/>
+      <c r="AP92" s="1"/>
+    </row>
+    <row r="93" spans="3:42">
+      <c r="C93" s="1"/>
+      <c r="N93" s="1"/>
+      <c r="V93" s="1"/>
+      <c r="X93" s="1"/>
+      <c r="Y93" s="13"/>
+      <c r="Z93" s="14"/>
+      <c r="AA93" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP93" s="1"/>
+    </row>
+    <row r="94" spans="3:42">
+      <c r="C94" s="1"/>
+      <c r="N94" s="1"/>
+      <c r="V94" s="1"/>
+      <c r="W94" s="13"/>
+      <c r="X94" s="14"/>
+      <c r="Z94" s="10"/>
+      <c r="AP94" s="1"/>
+    </row>
+    <row r="95" spans="3:42">
+      <c r="C95" s="1"/>
+      <c r="N95" s="1"/>
+      <c r="V95" s="1"/>
+      <c r="AP95" s="1"/>
+    </row>
+    <row r="96" spans="3:42">
+      <c r="C96" s="1"/>
+      <c r="N96" s="1"/>
+      <c r="V96" s="1"/>
+      <c r="AP96" s="1"/>
+    </row>
+    <row r="97" spans="3:42">
+      <c r="C97" s="1"/>
+      <c r="N97" s="1"/>
+      <c r="V97" s="1"/>
+      <c r="AP97" s="1"/>
+    </row>
+    <row r="98" spans="3:42">
+      <c r="C98" s="1"/>
+      <c r="N98" s="1"/>
+      <c r="V98" s="1"/>
+      <c r="AP98" s="1"/>
+    </row>
+    <row r="99" spans="3:42">
+      <c r="C99" s="1"/>
+      <c r="N99" s="1"/>
+      <c r="V99" s="1"/>
+      <c r="AP99" s="1"/>
+    </row>
+    <row r="100" spans="3:42">
+      <c r="C100" s="1"/>
+      <c r="N100" s="1"/>
+      <c r="V100" s="1"/>
+      <c r="AP100" s="1"/>
+    </row>
+    <row r="101" spans="3:42">
+      <c r="C101" s="1"/>
+      <c r="N101" s="1"/>
+      <c r="V101" s="1"/>
+      <c r="AP101" s="1"/>
+    </row>
+    <row r="102" spans="3:42">
+      <c r="C102" s="1"/>
+      <c r="N102" s="1"/>
+      <c r="V102" s="1"/>
+      <c r="AP102" s="1"/>
+    </row>
+    <row r="103" spans="3:42">
+      <c r="C103" s="1"/>
+      <c r="N103" s="1"/>
+      <c r="V103" s="1"/>
+      <c r="AP103" s="1"/>
+    </row>
+    <row r="104" spans="3:42">
+      <c r="C104" s="1"/>
+      <c r="N104" s="1"/>
+      <c r="V104" s="1"/>
+      <c r="AP104" s="1"/>
+    </row>
+    <row r="105" spans="3:42">
+      <c r="C105" s="1"/>
+      <c r="N105" s="1"/>
+      <c r="V105" s="1"/>
+      <c r="AP105" s="1"/>
+    </row>
+    <row r="106" spans="3:42">
+      <c r="C106" s="1"/>
+      <c r="N106" s="1"/>
+      <c r="V106" s="1"/>
+      <c r="AP106" s="1"/>
+    </row>
+    <row r="107" spans="3:42">
+      <c r="C107" s="1"/>
+      <c r="N107" s="1"/>
+      <c r="V107" s="1"/>
+      <c r="AP107" s="1"/>
+    </row>
+    <row r="108" spans="3:42">
+      <c r="C108" s="1"/>
+      <c r="N108" s="1"/>
+      <c r="V108" s="1"/>
+      <c r="AP108" s="1"/>
+    </row>
+    <row r="109" spans="3:42">
+      <c r="C109" s="1"/>
+      <c r="N109" s="1"/>
+      <c r="V109" s="1"/>
+      <c r="AP109" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="F7:L7"/>
-    <mergeCell ref="F8:L8"/>
+    <mergeCell ref="AB3:AI3"/>
+    <mergeCell ref="AM3:AS3"/>
+    <mergeCell ref="F7:K7"/>
+    <mergeCell ref="F8:K8"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="M3:S3"/>
-    <mergeCell ref="Z3:AC3"/>
-    <mergeCell ref="AI3:AP3"/>
-    <mergeCell ref="BA3:BG3"/>
+    <mergeCell ref="L3:R3"/>
+    <mergeCell ref="U3:X3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="C2:AR129"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="2" spans="3:43">
+      <c r="C2" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="22"/>
+      <c r="I2" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="22"/>
+      <c r="AL2" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="AM2" s="21"/>
+      <c r="AN2" s="21"/>
+      <c r="AO2" s="21"/>
+      <c r="AP2" s="21"/>
+      <c r="AQ2" s="22"/>
+    </row>
+    <row r="3" spans="3:43">
+      <c r="D3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="AN3" s="2"/>
+    </row>
+    <row r="4" spans="3:43">
+      <c r="D4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="AN4" s="1"/>
+    </row>
+    <row r="5" spans="3:43">
+      <c r="D5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="4"/>
+      <c r="AN5" s="1"/>
+    </row>
+    <row r="6" spans="3:43">
+      <c r="D6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="AN6" s="1"/>
+    </row>
+    <row r="7" spans="3:43">
+      <c r="D7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="M7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AN7" s="1"/>
+    </row>
+    <row r="8" spans="3:43">
+      <c r="D8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AN8" s="1"/>
+    </row>
+    <row r="9" spans="3:43">
+      <c r="D9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="AN9" s="1"/>
+    </row>
+    <row r="10" spans="3:43">
+      <c r="D10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="M10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN10" s="1"/>
+    </row>
+    <row r="11" spans="3:43">
+      <c r="D11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="M11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AN11" s="1"/>
+    </row>
+    <row r="12" spans="3:43">
+      <c r="D12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="O12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN12" s="1"/>
+    </row>
+    <row r="13" spans="3:43">
+      <c r="D13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="O13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN13" s="1"/>
+    </row>
+    <row r="14" spans="3:43">
+      <c r="D14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="4"/>
+      <c r="AN14" s="1"/>
+    </row>
+    <row r="15" spans="3:43">
+      <c r="D15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="2"/>
+      <c r="AN15" s="1"/>
+    </row>
+    <row r="16" spans="3:43">
+      <c r="D16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AN16" s="1"/>
+    </row>
+    <row r="17" spans="4:40">
+      <c r="D17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="1"/>
+      <c r="P17" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN17" s="1"/>
+    </row>
+    <row r="18" spans="4:40">
+      <c r="D18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="AN18" s="1"/>
+    </row>
+    <row r="19" spans="4:40">
+      <c r="D19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="O19" s="1"/>
+      <c r="AN19" s="1"/>
+    </row>
+    <row r="20" spans="4:40">
+      <c r="D20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" t="s">
+        <v>67</v>
+      </c>
+      <c r="O20" s="1"/>
+      <c r="AN20" s="1"/>
+    </row>
+    <row r="21" spans="4:40">
+      <c r="D21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" t="s">
+        <v>68</v>
+      </c>
+      <c r="O21" s="1"/>
+      <c r="AN21" s="1"/>
+    </row>
+    <row r="22" spans="4:40">
+      <c r="D22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="4"/>
+      <c r="AN22" s="1"/>
+    </row>
+    <row r="23" spans="4:40">
+      <c r="D23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="Q23" s="2"/>
+      <c r="AN23" s="1"/>
+    </row>
+    <row r="24" spans="4:40">
+      <c r="D24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="Q24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN24" s="1"/>
+    </row>
+    <row r="25" spans="4:40">
+      <c r="D25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="Q25" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN25" s="1"/>
+    </row>
+    <row r="26" spans="4:40">
+      <c r="D26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="Q26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN26" s="1"/>
+    </row>
+    <row r="27" spans="4:40">
+      <c r="D27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="Q27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AN27" s="1"/>
+    </row>
+    <row r="28" spans="4:40">
+      <c r="D28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="Q28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN28" s="1"/>
+    </row>
+    <row r="29" spans="4:40">
+      <c r="D29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="Q29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AN29" s="1"/>
+    </row>
+    <row r="30" spans="4:40">
+      <c r="D30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="Q30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN30" s="1"/>
+    </row>
+    <row r="31" spans="4:40">
+      <c r="D31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="AN31" s="1"/>
+    </row>
+    <row r="32" spans="4:40">
+      <c r="D32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="Q32" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN32" s="1"/>
+    </row>
+    <row r="33" spans="4:40">
+      <c r="D33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="S33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN33" s="1"/>
+    </row>
+    <row r="34" spans="4:40">
+      <c r="D34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="S34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN34" s="1"/>
+    </row>
+    <row r="35" spans="4:40">
+      <c r="D35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="S35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN35" s="1"/>
+    </row>
+    <row r="36" spans="4:40">
+      <c r="D36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+      <c r="U36" s="4"/>
+      <c r="AN36" s="1"/>
+    </row>
+    <row r="37" spans="4:40">
+      <c r="D37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="S37" s="2"/>
+      <c r="AN37" s="1"/>
+    </row>
+    <row r="38" spans="4:40">
+      <c r="D38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="S38" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN38" s="1"/>
+    </row>
+    <row r="39" spans="4:40">
+      <c r="D39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="S39" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN39" s="1"/>
+    </row>
+    <row r="40" spans="4:40">
+      <c r="D40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="AN40" s="1"/>
+    </row>
+    <row r="41" spans="4:40">
+      <c r="D41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="S41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN41" s="1"/>
+    </row>
+    <row r="42" spans="4:40">
+      <c r="D42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="U42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN42" s="1"/>
+    </row>
+    <row r="43" spans="4:40">
+      <c r="D43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="U43" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN43" s="1"/>
+    </row>
+    <row r="44" spans="4:40">
+      <c r="D44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="U44" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN44" s="1"/>
+    </row>
+    <row r="45" spans="4:40">
+      <c r="D45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="U45" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AN45" s="1"/>
+    </row>
+    <row r="46" spans="4:40">
+      <c r="D46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="4"/>
+      <c r="AN46" s="1"/>
+    </row>
+    <row r="47" spans="4:40">
+      <c r="D47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="U47" s="2"/>
+      <c r="AN47" s="1"/>
+    </row>
+    <row r="48" spans="4:40">
+      <c r="D48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="U48" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN48" s="1"/>
+    </row>
+    <row r="49" spans="4:40">
+      <c r="D49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="U49" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AN49" s="1"/>
+    </row>
+    <row r="50" spans="4:40">
+      <c r="D50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="S50" s="1"/>
+      <c r="U50" s="1"/>
+      <c r="AN50" s="1"/>
+    </row>
+    <row r="51" spans="4:40">
+      <c r="D51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="U51" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN51" s="1"/>
+    </row>
+    <row r="52" spans="4:40">
+      <c r="D52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="S52" s="1"/>
+      <c r="U52" s="1"/>
+      <c r="W52" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN52" s="1"/>
+    </row>
+    <row r="53" spans="4:40">
+      <c r="D53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="S53" s="1"/>
+      <c r="U53" s="1"/>
+      <c r="W53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN53" s="1"/>
+    </row>
+    <row r="54" spans="4:40">
+      <c r="D54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="S54" s="1"/>
+      <c r="U54" s="1"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="7"/>
+      <c r="X54" s="7"/>
+      <c r="Y54" s="4"/>
+      <c r="AN54" s="1"/>
+    </row>
+    <row r="55" spans="4:40">
+      <c r="D55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="S55" s="1"/>
+      <c r="U55" s="1"/>
+      <c r="V55" s="11"/>
+      <c r="W55" s="2"/>
+      <c r="AN55" s="1"/>
+    </row>
+    <row r="56" spans="4:40">
+      <c r="D56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="S56" s="1"/>
+      <c r="U56" s="1"/>
+      <c r="V56" s="12"/>
+      <c r="W56" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA56" s="28"/>
+      <c r="AN56" s="1"/>
+    </row>
+    <row r="57" spans="4:40">
+      <c r="D57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="S57" s="1"/>
+      <c r="U57" s="1"/>
+      <c r="V57" s="12"/>
+      <c r="W57" s="1"/>
+      <c r="AA57" s="28"/>
+      <c r="AN57" s="1"/>
+    </row>
+    <row r="58" spans="4:40">
+      <c r="D58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="S58" s="1"/>
+      <c r="U58" s="1"/>
+      <c r="V58" s="12"/>
+      <c r="W58" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA58" s="28"/>
+      <c r="AN58" s="1"/>
+    </row>
+    <row r="59" spans="4:40">
+      <c r="D59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="Q59" s="1"/>
+      <c r="S59" s="1"/>
+      <c r="U59" s="1"/>
+      <c r="V59" s="12"/>
+      <c r="W59" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA59" s="28"/>
+      <c r="AN59" s="1"/>
+    </row>
+    <row r="60" spans="4:40">
+      <c r="D60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="Q60" s="1"/>
+      <c r="S60" s="1"/>
+      <c r="U60" s="1"/>
+      <c r="V60" s="12"/>
+      <c r="W60" s="1"/>
+      <c r="X60" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA60" s="28"/>
+      <c r="AN60" s="1"/>
+    </row>
+    <row r="61" spans="4:40">
+      <c r="D61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="Q61" s="1"/>
+      <c r="S61" s="1"/>
+      <c r="U61" s="1"/>
+      <c r="V61" s="13"/>
+      <c r="W61" s="14"/>
+      <c r="AA61" s="28"/>
+      <c r="AN61" s="1"/>
+    </row>
+    <row r="62" spans="4:40">
+      <c r="D62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="Q62" s="1"/>
+      <c r="S62" s="1"/>
+      <c r="U62" s="1"/>
+      <c r="V62" s="12"/>
+      <c r="AA62" s="28"/>
+      <c r="AN62" s="1"/>
+    </row>
+    <row r="63" spans="4:40">
+      <c r="D63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="Q63" s="1"/>
+      <c r="S63" s="1"/>
+      <c r="U63" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="V63" s="12"/>
+      <c r="AA63" s="28"/>
+      <c r="AN63" s="1"/>
+    </row>
+    <row r="64" spans="4:40">
+      <c r="D64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="O64" s="1"/>
+      <c r="Q64" s="1"/>
+      <c r="S64" s="1"/>
+      <c r="U64" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="V64" s="12"/>
+      <c r="W64" s="1"/>
+      <c r="AA64" s="28"/>
+      <c r="AN64" s="1"/>
+    </row>
+    <row r="65" spans="4:44">
+      <c r="D65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="Q65" s="1"/>
+      <c r="S65" s="1"/>
+      <c r="U65" s="1"/>
+      <c r="V65" s="12"/>
+      <c r="W65" s="28"/>
+      <c r="AA65" s="28"/>
+      <c r="AN65" s="1"/>
+    </row>
+    <row r="66" spans="4:44">
+      <c r="D66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="Q66" s="1"/>
+      <c r="S66" s="1"/>
+      <c r="U66" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="V66" s="28"/>
+      <c r="W66" s="28"/>
+      <c r="AA66" s="28"/>
+      <c r="AN66" s="1"/>
+    </row>
+    <row r="67" spans="4:44">
+      <c r="D67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="Q67" s="1"/>
+      <c r="S67" s="1"/>
+      <c r="U67" s="1"/>
+      <c r="V67" s="28"/>
+      <c r="W67" s="28"/>
+      <c r="AA67" s="28"/>
+      <c r="AN67" s="1"/>
+    </row>
+    <row r="68" spans="4:44">
+      <c r="D68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="Q68" s="1"/>
+      <c r="S68" s="1"/>
+      <c r="U68" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN68" s="1"/>
+    </row>
+    <row r="69" spans="4:44">
+      <c r="D69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="Q69" s="1"/>
+      <c r="S69" s="1"/>
+      <c r="V69" s="3"/>
+      <c r="W69" s="7"/>
+      <c r="X69" s="7"/>
+      <c r="Y69" s="4"/>
+      <c r="AN69" s="1"/>
+    </row>
+    <row r="70" spans="4:44">
+      <c r="D70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="O70" s="1"/>
+      <c r="Q70" s="1"/>
+      <c r="S70" s="1"/>
+      <c r="U70" s="1"/>
+      <c r="V70" s="11"/>
+      <c r="W70" s="2"/>
+      <c r="AN70" s="1"/>
+    </row>
+    <row r="71" spans="4:44">
+      <c r="D71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="O71" s="1"/>
+      <c r="Q71" s="1"/>
+      <c r="S71" s="1"/>
+      <c r="U71" s="1"/>
+      <c r="V71" s="12"/>
+      <c r="W71" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AN71" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="72" spans="4:44">
+      <c r="D72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="O72" s="1"/>
+      <c r="Q72" s="1"/>
+      <c r="S72" s="1"/>
+      <c r="U72" s="1"/>
+      <c r="V72" s="12"/>
+      <c r="W72" s="1"/>
+      <c r="AN72" s="1"/>
+      <c r="AO72" s="3"/>
+      <c r="AP72" s="7"/>
+      <c r="AQ72" s="7"/>
+      <c r="AR72" s="4"/>
+    </row>
+    <row r="73" spans="4:44">
+      <c r="D73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="M73" s="1"/>
+      <c r="O73" s="1"/>
+      <c r="Q73" s="1"/>
+      <c r="S73" s="1"/>
+      <c r="U73" s="1"/>
+      <c r="V73" s="12"/>
+      <c r="W73" s="1"/>
+      <c r="AN73" s="1"/>
+      <c r="AP73" s="2"/>
+    </row>
+    <row r="74" spans="4:44">
+      <c r="D74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="M74" s="1"/>
+      <c r="O74" s="1"/>
+      <c r="Q74" s="1"/>
+      <c r="S74" s="1"/>
+      <c r="U74" s="1"/>
+      <c r="W74" s="1"/>
+      <c r="AN74" s="1"/>
+      <c r="AP74" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="75" spans="4:44">
+      <c r="D75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="O75" s="1"/>
+      <c r="Q75" s="1"/>
+      <c r="S75" s="1"/>
+      <c r="U75" s="1"/>
+      <c r="W75" s="1"/>
+      <c r="AN75" s="1"/>
+      <c r="AP75" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="76" spans="4:44">
+      <c r="D76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="M76" s="1"/>
+      <c r="O76" s="1"/>
+      <c r="Q76" s="1"/>
+      <c r="S76" s="1"/>
+      <c r="U76" s="1"/>
+      <c r="W76" s="1"/>
+      <c r="AN76" s="1"/>
+      <c r="AP76" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="77" spans="4:44">
+      <c r="D77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="Q77" s="1"/>
+      <c r="S77" s="1"/>
+      <c r="U77" s="1"/>
+      <c r="W77" s="1"/>
+      <c r="AN77" s="1"/>
+      <c r="AP77" s="1"/>
+    </row>
+    <row r="78" spans="4:44">
+      <c r="D78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="M78" s="1"/>
+      <c r="O78" s="1"/>
+      <c r="Q78" s="1"/>
+      <c r="S78" s="1"/>
+      <c r="U78" s="1"/>
+      <c r="W78" s="1"/>
+      <c r="AN78" s="1"/>
+      <c r="AP78" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="79" spans="4:44">
+      <c r="D79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="M79" s="1"/>
+      <c r="O79" s="1"/>
+      <c r="Q79" s="1"/>
+      <c r="S79" s="1"/>
+      <c r="U79" s="1"/>
+      <c r="W79" s="1"/>
+      <c r="AN79" s="1"/>
+      <c r="AP79" s="1"/>
+    </row>
+    <row r="80" spans="4:44">
+      <c r="D80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="M80" s="1"/>
+      <c r="O80" s="1"/>
+      <c r="Q80" s="1"/>
+      <c r="S80" s="1"/>
+      <c r="U80" s="1"/>
+      <c r="W80" s="1"/>
+      <c r="AN80" s="1"/>
+      <c r="AP80" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="81" spans="4:42">
+      <c r="D81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="M81" s="1"/>
+      <c r="O81" s="1"/>
+      <c r="Q81" s="1"/>
+      <c r="S81" s="1"/>
+      <c r="U81" s="1"/>
+      <c r="W81" s="1"/>
+      <c r="AN81" s="1"/>
+      <c r="AP81" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="82" spans="4:42">
+      <c r="D82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="M82" s="1"/>
+      <c r="O82" s="1"/>
+      <c r="Q82" s="1"/>
+      <c r="S82" s="1"/>
+      <c r="U82" s="1"/>
+      <c r="W82" s="1"/>
+      <c r="AN82" s="1"/>
+      <c r="AP82" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="83" spans="4:42">
+      <c r="D83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="M83" s="1"/>
+      <c r="O83" s="1"/>
+      <c r="Q83" s="1"/>
+      <c r="S83" s="1"/>
+      <c r="U83" s="1"/>
+      <c r="W83" s="1"/>
+      <c r="AN83" s="1"/>
+      <c r="AP83" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="84" spans="4:42">
+      <c r="D84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="M84" s="1"/>
+      <c r="O84" s="1"/>
+      <c r="Q84" s="1"/>
+      <c r="S84" s="1"/>
+      <c r="U84" s="1"/>
+      <c r="W84" s="1"/>
+      <c r="AN84" s="1"/>
+      <c r="AP84" s="1"/>
+    </row>
+    <row r="85" spans="4:42">
+      <c r="D85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="M85" s="1"/>
+      <c r="O85" s="1"/>
+      <c r="Q85" s="1"/>
+      <c r="S85" s="1"/>
+      <c r="U85" s="1"/>
+      <c r="W85" s="1"/>
+      <c r="AN85" s="1"/>
+      <c r="AP85" s="1"/>
+    </row>
+    <row r="86" spans="4:42">
+      <c r="D86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="M86" s="1"/>
+      <c r="O86" s="1"/>
+      <c r="Q86" s="1"/>
+      <c r="S86" s="1"/>
+      <c r="U86" s="1"/>
+      <c r="W86" s="1"/>
+      <c r="AN86" s="1"/>
+      <c r="AP86" s="1"/>
+    </row>
+    <row r="87" spans="4:42">
+      <c r="D87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="M87" s="1"/>
+      <c r="O87" s="1"/>
+      <c r="Q87" s="1"/>
+      <c r="S87" s="1"/>
+      <c r="U87" s="1"/>
+      <c r="W87" s="1"/>
+      <c r="AN87" s="1"/>
+      <c r="AP87" s="1"/>
+    </row>
+    <row r="88" spans="4:42">
+      <c r="D88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="M88" s="1"/>
+      <c r="O88" s="1"/>
+      <c r="Q88" s="1"/>
+      <c r="S88" s="1"/>
+      <c r="U88" s="1"/>
+      <c r="W88" s="1"/>
+      <c r="AN88" s="1"/>
+      <c r="AP88" s="1"/>
+    </row>
+    <row r="89" spans="4:42">
+      <c r="D89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="M89" s="1"/>
+      <c r="O89" s="1"/>
+      <c r="Q89" s="1"/>
+      <c r="S89" s="1"/>
+      <c r="U89" s="1"/>
+      <c r="W89" s="1"/>
+      <c r="AN89" s="1"/>
+      <c r="AP89" s="1"/>
+    </row>
+    <row r="90" spans="4:42">
+      <c r="D90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="M90" s="1"/>
+      <c r="O90" s="1"/>
+      <c r="Q90" s="1"/>
+      <c r="S90" s="1"/>
+      <c r="U90" s="1"/>
+      <c r="W90" s="1"/>
+      <c r="AN90" s="1"/>
+      <c r="AP90" s="1"/>
+    </row>
+    <row r="91" spans="4:42">
+      <c r="D91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="M91" s="1"/>
+      <c r="O91" s="1"/>
+      <c r="Q91" s="1"/>
+      <c r="S91" s="1"/>
+      <c r="U91" s="1"/>
+      <c r="W91" s="1"/>
+      <c r="AN91" s="1"/>
+      <c r="AP91" s="1"/>
+    </row>
+    <row r="92" spans="4:42">
+      <c r="D92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="M92" s="1"/>
+      <c r="O92" s="1"/>
+      <c r="Q92" s="1"/>
+      <c r="S92" s="1"/>
+      <c r="U92" s="1"/>
+      <c r="W92" s="1"/>
+      <c r="AN92" s="1"/>
+      <c r="AP92" s="1"/>
+    </row>
+    <row r="93" spans="4:42">
+      <c r="D93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="M93" s="1"/>
+      <c r="O93" s="1"/>
+      <c r="Q93" s="1"/>
+      <c r="S93" s="1"/>
+      <c r="U93" s="1"/>
+      <c r="W93" s="1"/>
+      <c r="AN93" s="1"/>
+      <c r="AP93" s="1"/>
+    </row>
+    <row r="94" spans="4:42">
+      <c r="D94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="M94" s="1"/>
+      <c r="O94" s="1"/>
+      <c r="Q94" s="1"/>
+      <c r="S94" s="1"/>
+      <c r="U94" s="1"/>
+      <c r="W94" s="1"/>
+      <c r="AN94" s="1"/>
+      <c r="AP94" s="1"/>
+    </row>
+    <row r="95" spans="4:42">
+      <c r="D95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="M95" s="1"/>
+      <c r="O95" s="1"/>
+      <c r="Q95" s="1"/>
+      <c r="S95" s="1"/>
+      <c r="U95" s="1"/>
+      <c r="W95" s="1"/>
+      <c r="AN95" s="1"/>
+      <c r="AP95" s="1"/>
+    </row>
+    <row r="96" spans="4:42">
+      <c r="D96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="M96" s="1"/>
+      <c r="O96" s="1"/>
+      <c r="Q96" s="1"/>
+      <c r="S96" s="1"/>
+      <c r="U96" s="1"/>
+      <c r="W96" s="1"/>
+      <c r="AN96" s="1"/>
+      <c r="AP96" s="1"/>
+    </row>
+    <row r="97" spans="4:42">
+      <c r="D97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="M97" s="1"/>
+      <c r="O97" s="1"/>
+      <c r="Q97" s="1"/>
+      <c r="S97" s="1"/>
+      <c r="U97" s="1"/>
+      <c r="W97" s="1"/>
+      <c r="AN97" s="1"/>
+      <c r="AP97" s="1"/>
+    </row>
+    <row r="98" spans="4:42">
+      <c r="D98" s="1"/>
+      <c r="K98" s="1"/>
+      <c r="M98" s="1"/>
+      <c r="O98" s="1"/>
+      <c r="Q98" s="1"/>
+      <c r="S98" s="1"/>
+      <c r="U98" s="1"/>
+      <c r="W98" s="1"/>
+      <c r="AN98" s="1"/>
+      <c r="AP98" s="1"/>
+    </row>
+    <row r="99" spans="4:42">
+      <c r="D99" s="1"/>
+      <c r="K99" s="1"/>
+      <c r="M99" s="1"/>
+      <c r="O99" s="1"/>
+      <c r="Q99" s="1"/>
+      <c r="S99" s="1"/>
+      <c r="U99" s="1"/>
+      <c r="W99" s="1"/>
+      <c r="AN99" s="1"/>
+      <c r="AP99" s="1"/>
+    </row>
+    <row r="100" spans="4:42">
+      <c r="D100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="M100" s="1"/>
+      <c r="O100" s="1"/>
+      <c r="Q100" s="1"/>
+      <c r="S100" s="1"/>
+      <c r="U100" s="1"/>
+      <c r="W100" s="1"/>
+      <c r="AN100" s="1"/>
+      <c r="AP100" s="1"/>
+    </row>
+    <row r="101" spans="4:42">
+      <c r="D101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="M101" s="1"/>
+      <c r="O101" s="1"/>
+      <c r="Q101" s="1"/>
+      <c r="S101" s="1"/>
+      <c r="U101" s="1"/>
+      <c r="W101" s="1"/>
+      <c r="AN101" s="1"/>
+      <c r="AP101" s="1"/>
+    </row>
+    <row r="102" spans="4:42">
+      <c r="D102" s="1"/>
+      <c r="K102" s="1"/>
+      <c r="M102" s="1"/>
+      <c r="O102" s="1"/>
+      <c r="Q102" s="1"/>
+      <c r="S102" s="1"/>
+      <c r="U102" s="1"/>
+      <c r="W102" s="1"/>
+      <c r="AN102" s="1"/>
+      <c r="AP102" s="1"/>
+    </row>
+    <row r="103" spans="4:42">
+      <c r="D103" s="1"/>
+      <c r="K103" s="1"/>
+      <c r="M103" s="1"/>
+      <c r="O103" s="1"/>
+      <c r="Q103" s="1"/>
+      <c r="S103" s="1"/>
+      <c r="U103" s="1"/>
+      <c r="W103" s="1"/>
+      <c r="AN103" s="1"/>
+      <c r="AP103" s="1"/>
+    </row>
+    <row r="104" spans="4:42">
+      <c r="D104" s="1"/>
+      <c r="K104" s="1"/>
+      <c r="M104" s="1"/>
+      <c r="O104" s="1"/>
+      <c r="Q104" s="1"/>
+      <c r="S104" s="1"/>
+      <c r="U104" s="1"/>
+      <c r="W104" s="1"/>
+      <c r="AN104" s="1"/>
+      <c r="AP104" s="1"/>
+    </row>
+    <row r="105" spans="4:42">
+      <c r="D105" s="1"/>
+      <c r="K105" s="1"/>
+      <c r="M105" s="1"/>
+      <c r="O105" s="1"/>
+      <c r="Q105" s="1"/>
+      <c r="S105" s="1"/>
+      <c r="U105" s="1"/>
+      <c r="W105" s="1"/>
+      <c r="AN105" s="1"/>
+      <c r="AP105" s="1"/>
+    </row>
+    <row r="106" spans="4:42">
+      <c r="D106" s="1"/>
+      <c r="K106" s="1"/>
+      <c r="M106" s="1"/>
+      <c r="O106" s="1"/>
+      <c r="Q106" s="1"/>
+      <c r="S106" s="1"/>
+      <c r="U106" s="1"/>
+      <c r="W106" s="1"/>
+      <c r="AN106" s="1"/>
+      <c r="AP106" s="1"/>
+    </row>
+    <row r="107" spans="4:42">
+      <c r="D107" s="1"/>
+      <c r="K107" s="1"/>
+      <c r="M107" s="1"/>
+      <c r="O107" s="1"/>
+      <c r="Q107" s="1"/>
+      <c r="S107" s="1"/>
+      <c r="U107" s="1"/>
+      <c r="W107" s="1"/>
+      <c r="AN107" s="1"/>
+      <c r="AP107" s="1"/>
+    </row>
+    <row r="108" spans="4:42">
+      <c r="D108" s="1"/>
+      <c r="K108" s="1"/>
+      <c r="M108" s="1"/>
+      <c r="O108" s="1"/>
+      <c r="Q108" s="1"/>
+      <c r="S108" s="1"/>
+      <c r="U108" s="1"/>
+      <c r="W108" s="1"/>
+      <c r="AN108" s="1"/>
+      <c r="AP108" s="1"/>
+    </row>
+    <row r="109" spans="4:42">
+      <c r="D109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="M109" s="1"/>
+      <c r="O109" s="1"/>
+      <c r="Q109" s="1"/>
+      <c r="S109" s="1"/>
+      <c r="U109" s="1"/>
+      <c r="W109" s="1"/>
+      <c r="AN109" s="1"/>
+      <c r="AP109" s="1"/>
+    </row>
+    <row r="110" spans="4:42">
+      <c r="D110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="M110" s="1"/>
+      <c r="O110" s="1"/>
+      <c r="Q110" s="1"/>
+      <c r="S110" s="1"/>
+      <c r="U110" s="1"/>
+      <c r="W110" s="1"/>
+      <c r="AN110" s="1"/>
+      <c r="AP110" s="1"/>
+    </row>
+    <row r="111" spans="4:42">
+      <c r="D111" s="1"/>
+      <c r="K111" s="1"/>
+      <c r="M111" s="1"/>
+      <c r="O111" s="1"/>
+      <c r="Q111" s="1"/>
+      <c r="S111" s="1"/>
+      <c r="U111" s="1"/>
+      <c r="W111" s="1"/>
+      <c r="AN111" s="1"/>
+      <c r="AP111" s="1"/>
+    </row>
+    <row r="112" spans="4:42">
+      <c r="D112" s="1"/>
+      <c r="K112" s="1"/>
+      <c r="M112" s="1"/>
+      <c r="O112" s="1"/>
+      <c r="Q112" s="1"/>
+      <c r="S112" s="1"/>
+      <c r="U112" s="1"/>
+      <c r="W112" s="1"/>
+      <c r="AN112" s="1"/>
+      <c r="AP112" s="1"/>
+    </row>
+    <row r="113" spans="4:42">
+      <c r="D113" s="1"/>
+      <c r="K113" s="1"/>
+      <c r="M113" s="1"/>
+      <c r="O113" s="1"/>
+      <c r="Q113" s="1"/>
+      <c r="S113" s="1"/>
+      <c r="U113" s="1"/>
+      <c r="W113" s="1"/>
+      <c r="AN113" s="1"/>
+      <c r="AP113" s="1"/>
+    </row>
+    <row r="114" spans="4:42">
+      <c r="D114" s="1"/>
+      <c r="K114" s="1"/>
+      <c r="M114" s="1"/>
+      <c r="O114" s="1"/>
+      <c r="Q114" s="1"/>
+      <c r="S114" s="1"/>
+      <c r="U114" s="1"/>
+      <c r="W114" s="1"/>
+      <c r="AN114" s="1"/>
+      <c r="AP114" s="1"/>
+    </row>
+    <row r="115" spans="4:42">
+      <c r="D115" s="1"/>
+      <c r="K115" s="1"/>
+      <c r="M115" s="1"/>
+      <c r="O115" s="1"/>
+      <c r="Q115" s="1"/>
+      <c r="S115" s="1"/>
+      <c r="U115" s="1"/>
+      <c r="W115" s="1"/>
+      <c r="AN115" s="1"/>
+      <c r="AP115" s="1"/>
+    </row>
+    <row r="116" spans="4:42">
+      <c r="D116" s="1"/>
+      <c r="K116" s="1"/>
+      <c r="M116" s="1"/>
+      <c r="O116" s="1"/>
+      <c r="Q116" s="1"/>
+      <c r="S116" s="1"/>
+      <c r="U116" s="1"/>
+      <c r="W116" s="1"/>
+      <c r="AN116" s="1"/>
+      <c r="AP116" s="1"/>
+    </row>
+    <row r="117" spans="4:42">
+      <c r="D117" s="1"/>
+      <c r="K117" s="1"/>
+      <c r="M117" s="1"/>
+      <c r="O117" s="1"/>
+      <c r="Q117" s="1"/>
+      <c r="S117" s="1"/>
+      <c r="U117" s="1"/>
+      <c r="W117" s="1"/>
+      <c r="AN117" s="1"/>
+      <c r="AP117" s="1"/>
+    </row>
+    <row r="118" spans="4:42">
+      <c r="D118" s="1"/>
+      <c r="K118" s="1"/>
+      <c r="M118" s="1"/>
+      <c r="O118" s="1"/>
+      <c r="Q118" s="1"/>
+      <c r="S118" s="1"/>
+      <c r="U118" s="1"/>
+      <c r="W118" s="1"/>
+      <c r="AN118" s="1"/>
+      <c r="AP118" s="1"/>
+    </row>
+    <row r="119" spans="4:42">
+      <c r="D119" s="1"/>
+      <c r="K119" s="1"/>
+      <c r="M119" s="1"/>
+      <c r="O119" s="1"/>
+      <c r="Q119" s="1"/>
+      <c r="S119" s="1"/>
+      <c r="U119" s="1"/>
+      <c r="W119" s="1"/>
+      <c r="AN119" s="1"/>
+      <c r="AP119" s="1"/>
+    </row>
+    <row r="120" spans="4:42">
+      <c r="D120" s="1"/>
+      <c r="K120" s="1"/>
+      <c r="M120" s="1"/>
+      <c r="O120" s="1"/>
+      <c r="Q120" s="1"/>
+      <c r="S120" s="1"/>
+      <c r="U120" s="1"/>
+      <c r="W120" s="1"/>
+      <c r="AN120" s="1"/>
+      <c r="AP120" s="1"/>
+    </row>
+    <row r="121" spans="4:42">
+      <c r="D121" s="1"/>
+      <c r="K121" s="1"/>
+      <c r="M121" s="1"/>
+      <c r="O121" s="1"/>
+      <c r="Q121" s="1"/>
+      <c r="S121" s="1"/>
+      <c r="U121" s="1"/>
+      <c r="W121" s="1"/>
+      <c r="AN121" s="1"/>
+      <c r="AP121" s="1"/>
+    </row>
+    <row r="122" spans="4:42">
+      <c r="D122" s="1"/>
+      <c r="K122" s="1"/>
+      <c r="M122" s="1"/>
+      <c r="O122" s="1"/>
+      <c r="Q122" s="1"/>
+      <c r="S122" s="1"/>
+      <c r="U122" s="1"/>
+      <c r="W122" s="1"/>
+      <c r="AN122" s="1"/>
+      <c r="AP122" s="1"/>
+    </row>
+    <row r="123" spans="4:42">
+      <c r="D123" s="1"/>
+      <c r="K123" s="1"/>
+      <c r="M123" s="1"/>
+      <c r="O123" s="1"/>
+      <c r="Q123" s="1"/>
+      <c r="S123" s="1"/>
+      <c r="U123" s="1"/>
+      <c r="W123" s="1"/>
+      <c r="AN123" s="1"/>
+      <c r="AP123" s="1"/>
+    </row>
+    <row r="124" spans="4:42">
+      <c r="D124" s="1"/>
+      <c r="K124" s="1"/>
+      <c r="M124" s="1"/>
+      <c r="O124" s="1"/>
+      <c r="Q124" s="1"/>
+      <c r="S124" s="1"/>
+      <c r="U124" s="1"/>
+      <c r="W124" s="1"/>
+      <c r="AN124" s="1"/>
+      <c r="AP124" s="1"/>
+    </row>
+    <row r="125" spans="4:42">
+      <c r="D125" s="1"/>
+      <c r="K125" s="1"/>
+      <c r="M125" s="1"/>
+      <c r="O125" s="1"/>
+      <c r="Q125" s="1"/>
+      <c r="S125" s="1"/>
+      <c r="U125" s="1"/>
+      <c r="W125" s="1"/>
+      <c r="AN125" s="1"/>
+      <c r="AP125" s="1"/>
+    </row>
+    <row r="126" spans="4:42">
+      <c r="D126" s="1"/>
+      <c r="K126" s="1"/>
+      <c r="M126" s="1"/>
+      <c r="O126" s="1"/>
+      <c r="Q126" s="1"/>
+      <c r="S126" s="1"/>
+      <c r="U126" s="1"/>
+      <c r="W126" s="1"/>
+      <c r="AN126" s="1"/>
+      <c r="AP126" s="1"/>
+    </row>
+    <row r="127" spans="4:42">
+      <c r="D127" s="1"/>
+      <c r="K127" s="1"/>
+      <c r="M127" s="1"/>
+      <c r="O127" s="1"/>
+      <c r="Q127" s="1"/>
+      <c r="S127" s="1"/>
+      <c r="U127" s="1"/>
+      <c r="W127" s="1"/>
+      <c r="AN127" s="1"/>
+      <c r="AP127" s="1"/>
+    </row>
+    <row r="128" spans="4:42">
+      <c r="D128" s="1"/>
+      <c r="K128" s="1"/>
+      <c r="M128" s="1"/>
+      <c r="O128" s="1"/>
+      <c r="Q128" s="1"/>
+      <c r="S128" s="1"/>
+      <c r="U128" s="1"/>
+      <c r="W128" s="1"/>
+      <c r="AN128" s="1"/>
+      <c r="AP128" s="1"/>
+    </row>
+    <row r="129" spans="4:42">
+      <c r="D129" s="1"/>
+      <c r="K129" s="1"/>
+      <c r="M129" s="1"/>
+      <c r="O129" s="1"/>
+      <c r="Q129" s="1"/>
+      <c r="S129" s="1"/>
+      <c r="U129" s="1"/>
+      <c r="W129" s="1"/>
+      <c r="AN129" s="1"/>
+      <c r="AP129" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="I2:N2"/>
+    <mergeCell ref="AL2:AQ2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>